--- a/jogos_2025-07-14.xlsx
+++ b/jogos_2025-07-14.xlsx
@@ -184,12 +184,12 @@
     <t>ÍBV</t>
   </si>
   <si>
+    <t>Afturelding</t>
+  </si>
+  <si>
     <t>ÍA</t>
   </si>
   <si>
-    <t>Afturelding</t>
-  </si>
-  <si>
     <t>Deportivo Riestra</t>
   </si>
   <si>
@@ -199,21 +199,21 @@
     <t>Banfield</t>
   </si>
   <si>
+    <t>Retrô</t>
+  </si>
+  <si>
     <t>Maringá</t>
   </si>
   <si>
-    <t>Retrô</t>
-  </si>
-  <si>
     <t>Juventude</t>
   </si>
   <si>
+    <t>Vélez Sarsfield</t>
+  </si>
+  <si>
     <t>Unión Santa Fe</t>
   </si>
   <si>
-    <t>Vélez Sarsfield</t>
-  </si>
-  <si>
     <t>Botafogo SP</t>
   </si>
   <si>
@@ -223,12 +223,12 @@
     <t>Stjarnan</t>
   </si>
   <si>
+    <t>Fram</t>
+  </si>
+  <si>
     <t>KR</t>
   </si>
   <si>
-    <t>Fram</t>
-  </si>
-  <si>
     <t>Lanús</t>
   </si>
   <si>
@@ -238,19 +238,19 @@
     <t>Defensa y Justicia</t>
   </si>
   <si>
+    <t>CSA</t>
+  </si>
+  <si>
     <t>Brusque</t>
   </si>
   <si>
-    <t>CSA</t>
-  </si>
-  <si>
     <t>Sport Recife</t>
   </si>
   <si>
+    <t>Tigre</t>
+  </si>
+  <si>
     <t>Estudiantes</t>
-  </si>
-  <si>
-    <t>Tigre</t>
   </si>
   <si>
     <t>Volta Redonda</t>
@@ -914,34 +914,34 @@
         <v>1.88</v>
       </c>
       <c r="R3">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S3">
         <v>3.3</v>
       </c>
       <c r="T3">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="U3">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="V3">
         <v>5</v>
       </c>
       <c r="W3">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="X3">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y3">
         <v>9.5</v>
       </c>
       <c r="Z3">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AA3">
-        <v>4.5</v>
+        <v>4.71</v>
       </c>
       <c r="AB3">
         <v>1.53</v>
@@ -950,22 +950,22 @@
         <v>2.25</v>
       </c>
       <c r="AD3">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="AE3">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AF3">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="AG3">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="AH3">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="AI3">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AJ3" t="s">
         <v>82</v>
@@ -1009,79 +1009,79 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L4">
-        <v>3.95</v>
+        <v>2.5</v>
       </c>
       <c r="M4">
-        <v>4.5</v>
+        <v>3.54</v>
       </c>
       <c r="N4">
-        <v>1.6</v>
+        <v>2.68</v>
       </c>
       <c r="O4">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="P4">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="Q4">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="R4">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="S4">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="V4">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="W4">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y4">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Z4">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AA4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AB4">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AC4">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AD4">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AE4">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF4">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="AH4">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="s">
         <v>82</v>
@@ -1125,79 +1125,79 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L5">
-        <v>2.5</v>
+        <v>3.95</v>
       </c>
       <c r="M5">
-        <v>3.54</v>
+        <v>4.5</v>
       </c>
       <c r="N5">
-        <v>2.68</v>
+        <v>1.6</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AJ5" t="s">
         <v>82</v>
@@ -1378,28 +1378,28 @@
         <v>2.4</v>
       </c>
       <c r="R7">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="S7">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="T7">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="U7">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="V7">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="W7">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X7">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Y7">
-        <v>6.35</v>
+        <v>6</v>
       </c>
       <c r="Z7">
         <v>1.48</v>
@@ -1414,22 +1414,22 @@
         <v>1.5</v>
       </c>
       <c r="AD7">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="AE7">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF7">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AG7">
         <v>1.73</v>
       </c>
       <c r="AH7">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AI7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AJ7" t="s">
         <v>82</v>
@@ -1592,76 +1592,76 @@
         <v>80</v>
       </c>
       <c r="L9">
-        <v>1.88</v>
+        <v>2.44</v>
       </c>
       <c r="M9">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="N9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O9">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="P9">
-        <v>8.1</v>
+        <v>5.5</v>
       </c>
       <c r="Q9">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="R9">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="S9">
-        <v>2.6</v>
+        <v>2.13</v>
       </c>
       <c r="T9">
-        <v>3.18</v>
+        <v>3.75</v>
       </c>
       <c r="U9">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W9">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X9">
+        <v>1.11</v>
+      </c>
+      <c r="Y9">
+        <v>5.5</v>
+      </c>
+      <c r="Z9">
+        <v>1.48</v>
+      </c>
+      <c r="AA9">
+        <v>2.37</v>
+      </c>
+      <c r="AB9">
+        <v>2.69</v>
+      </c>
+      <c r="AC9">
+        <v>1.42</v>
+      </c>
+      <c r="AD9">
+        <v>5.35</v>
+      </c>
+      <c r="AE9">
+        <v>1.12</v>
+      </c>
+      <c r="AF9">
+        <v>2.2</v>
+      </c>
+      <c r="AG9">
+        <v>1.62</v>
+      </c>
+      <c r="AH9">
+        <v>11.5</v>
+      </c>
+      <c r="AI9">
         <v>1.02</v>
-      </c>
-      <c r="Y9">
-        <v>8.1</v>
-      </c>
-      <c r="Z9">
-        <v>1.34</v>
-      </c>
-      <c r="AA9">
-        <v>2.78</v>
-      </c>
-      <c r="AB9">
-        <v>2.2</v>
-      </c>
-      <c r="AC9">
-        <v>1.6</v>
-      </c>
-      <c r="AD9">
-        <v>4</v>
-      </c>
-      <c r="AE9">
-        <v>1.17</v>
-      </c>
-      <c r="AF9">
-        <v>2.05</v>
-      </c>
-      <c r="AG9">
-        <v>1.7</v>
-      </c>
-      <c r="AH9">
-        <v>8.4</v>
-      </c>
-      <c r="AI9">
-        <v>1.01</v>
       </c>
       <c r="AJ9" t="s">
         <v>82</v>
@@ -1708,28 +1708,28 @@
         <v>80</v>
       </c>
       <c r="L10">
-        <v>2.45</v>
+        <v>1.67</v>
       </c>
       <c r="M10">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="N10">
-        <v>2.7</v>
+        <v>5</v>
       </c>
       <c r="O10">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="P10">
-        <v>5.5</v>
+        <v>8.1</v>
       </c>
       <c r="Q10">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="R10">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="S10">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="T10">
         <v>3.6</v>
@@ -1738,43 +1738,43 @@
         <v>1.25</v>
       </c>
       <c r="V10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W10">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X10">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="Y10">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="Z10">
+        <v>1.5</v>
+      </c>
+      <c r="AA10">
+        <v>2.4</v>
+      </c>
+      <c r="AB10">
+        <v>2.38</v>
+      </c>
+      <c r="AC10">
         <v>1.48</v>
       </c>
-      <c r="AA10">
-        <v>2.37</v>
-      </c>
-      <c r="AB10">
-        <v>2.49</v>
-      </c>
-      <c r="AC10">
-        <v>1.44</v>
-      </c>
       <c r="AD10">
-        <v>4.9</v>
+        <v>4.75</v>
       </c>
       <c r="AE10">
         <v>1.15</v>
       </c>
       <c r="AF10">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AG10">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AH10">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AI10">
         <v>1.02</v>
@@ -1824,19 +1824,19 @@
         <v>80</v>
       </c>
       <c r="L11">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="M11">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="N11">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="O11">
         <v>1.83</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>7.25</v>
       </c>
       <c r="Q11">
         <v>2.25</v>
@@ -1854,13 +1854,13 @@
         <v>1.33</v>
       </c>
       <c r="V11">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W11">
         <v>1.06</v>
       </c>
       <c r="X11">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="Y11">
         <v>7.5</v>
@@ -1869,16 +1869,16 @@
         <v>1.4</v>
       </c>
       <c r="AA11">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="AB11">
         <v>2.25</v>
       </c>
       <c r="AC11">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AD11">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AE11">
         <v>1.2</v>
@@ -1890,10 +1890,10 @@
         <v>1.85</v>
       </c>
       <c r="AH11">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="AI11">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AJ11" t="s">
         <v>82</v>
@@ -1940,76 +1940,76 @@
         <v>80</v>
       </c>
       <c r="L12">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="M12">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="N12">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="O12">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="P12">
+        <v>5</v>
+      </c>
+      <c r="Q12">
+        <v>2.88</v>
+      </c>
+      <c r="R12">
+        <v>1.67</v>
+      </c>
+      <c r="S12">
+        <v>2.1</v>
+      </c>
+      <c r="T12">
+        <v>4.33</v>
+      </c>
+      <c r="U12">
+        <v>1.2</v>
+      </c>
+      <c r="V12">
+        <v>15</v>
+      </c>
+      <c r="W12">
+        <v>1.03</v>
+      </c>
+      <c r="X12">
+        <v>1.14</v>
+      </c>
+      <c r="Y12">
+        <v>5.5</v>
+      </c>
+      <c r="Z12">
+        <v>1.58</v>
+      </c>
+      <c r="AA12">
+        <v>2.18</v>
+      </c>
+      <c r="AB12">
+        <v>3.1</v>
+      </c>
+      <c r="AC12">
+        <v>1.36</v>
+      </c>
+      <c r="AD12">
         <v>6.5</v>
       </c>
-      <c r="Q12">
-        <v>2.25</v>
-      </c>
-      <c r="R12">
-        <v>1.53</v>
-      </c>
-      <c r="S12">
-        <v>2.38</v>
-      </c>
-      <c r="T12">
-        <v>3.5</v>
-      </c>
-      <c r="U12">
-        <v>1.29</v>
-      </c>
-      <c r="V12">
+      <c r="AE12">
+        <v>1.1</v>
+      </c>
+      <c r="AF12">
+        <v>2.5</v>
+      </c>
+      <c r="AG12">
+        <v>1.5</v>
+      </c>
+      <c r="AH12">
         <v>11</v>
       </c>
-      <c r="W12">
-        <v>1.05</v>
-      </c>
-      <c r="X12">
-        <v>1.1</v>
-      </c>
-      <c r="Y12">
-        <v>6.5</v>
-      </c>
-      <c r="Z12">
-        <v>1.48</v>
-      </c>
-      <c r="AA12">
-        <v>2.43</v>
-      </c>
-      <c r="AB12">
-        <v>2.5</v>
-      </c>
-      <c r="AC12">
-        <v>1.5</v>
-      </c>
-      <c r="AD12">
-        <v>5</v>
-      </c>
-      <c r="AE12">
-        <v>1.17</v>
-      </c>
-      <c r="AF12">
-        <v>2</v>
-      </c>
-      <c r="AG12">
-        <v>1.75</v>
-      </c>
-      <c r="AH12">
-        <v>9.5</v>
-      </c>
       <c r="AI12">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AJ12" t="s">
         <v>82</v>
@@ -2056,76 +2056,76 @@
         <v>80</v>
       </c>
       <c r="L13">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="M13">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="N13">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="O13">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="P13">
+        <v>6.5</v>
+      </c>
+      <c r="Q13">
+        <v>2.25</v>
+      </c>
+      <c r="R13">
+        <v>1.53</v>
+      </c>
+      <c r="S13">
+        <v>2.38</v>
+      </c>
+      <c r="T13">
+        <v>3.5</v>
+      </c>
+      <c r="U13">
+        <v>1.29</v>
+      </c>
+      <c r="V13">
+        <v>11</v>
+      </c>
+      <c r="W13">
+        <v>1.05</v>
+      </c>
+      <c r="X13">
+        <v>1.1</v>
+      </c>
+      <c r="Y13">
+        <v>6.5</v>
+      </c>
+      <c r="Z13">
+        <v>1.48</v>
+      </c>
+      <c r="AA13">
+        <v>2.43</v>
+      </c>
+      <c r="AB13">
+        <v>2.5</v>
+      </c>
+      <c r="AC13">
+        <v>1.5</v>
+      </c>
+      <c r="AD13">
         <v>5</v>
       </c>
-      <c r="Q13">
-        <v>2.88</v>
-      </c>
-      <c r="R13">
-        <v>1.67</v>
-      </c>
-      <c r="S13">
-        <v>2.1</v>
-      </c>
-      <c r="T13">
-        <v>4.33</v>
-      </c>
-      <c r="U13">
-        <v>1.2</v>
-      </c>
-      <c r="V13">
-        <v>15</v>
-      </c>
-      <c r="W13">
-        <v>1.03</v>
-      </c>
-      <c r="X13">
-        <v>1.14</v>
-      </c>
-      <c r="Y13">
-        <v>5.5</v>
-      </c>
-      <c r="Z13">
-        <v>1.58</v>
-      </c>
-      <c r="AA13">
-        <v>2.18</v>
-      </c>
-      <c r="AB13">
-        <v>3.1</v>
-      </c>
-      <c r="AC13">
-        <v>1.36</v>
-      </c>
-      <c r="AD13">
-        <v>6.5</v>
-      </c>
       <c r="AE13">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AF13">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AG13">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AH13">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="AI13">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AJ13" t="s">
         <v>82</v>
@@ -2196,7 +2196,7 @@
         <v>2.3</v>
       </c>
       <c r="T14">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="U14">
         <v>1.22</v>
@@ -2208,7 +2208,7 @@
         <v>1.04</v>
       </c>
       <c r="X14">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Y14">
         <v>5.5</v>
@@ -2226,7 +2226,7 @@
         <v>1.36</v>
       </c>
       <c r="AD14">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AE14">
         <v>1.11</v>
@@ -2238,10 +2238,10 @@
         <v>1.57</v>
       </c>
       <c r="AH14">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AI14">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AJ14" t="s">
         <v>82</v>

--- a/jogos_2025-07-14.xlsx
+++ b/jogos_2025-07-14.xlsx
@@ -896,13 +896,13 @@
         <v>80</v>
       </c>
       <c r="L3">
-        <v>2.75</v>
+        <v>3.05</v>
       </c>
       <c r="M3">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N3">
-        <v>2.27</v>
+        <v>2.12</v>
       </c>
       <c r="O3">
         <v>1.98</v>
@@ -914,16 +914,16 @@
         <v>1.88</v>
       </c>
       <c r="R3">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S3">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="T3">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="U3">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="V3">
         <v>5</v>
@@ -935,34 +935,34 @@
         <v>1.03</v>
       </c>
       <c r="Y3">
-        <v>9.5</v>
+        <v>12</v>
       </c>
       <c r="Z3">
         <v>1.14</v>
       </c>
       <c r="AA3">
-        <v>4.71</v>
+        <v>4.75</v>
       </c>
       <c r="AB3">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AC3">
         <v>2.25</v>
       </c>
       <c r="AD3">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="AE3">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AF3">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AG3">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AH3">
-        <v>3.98</v>
+        <v>4.3</v>
       </c>
       <c r="AI3">
         <v>1.2</v>
@@ -1012,13 +1012,13 @@
         <v>81</v>
       </c>
       <c r="L4">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="M4">
-        <v>3.54</v>
+        <v>3.51</v>
       </c>
       <c r="N4">
-        <v>2.68</v>
+        <v>2.63</v>
       </c>
       <c r="O4">
         <v>0</v>
@@ -1128,13 +1128,13 @@
         <v>80</v>
       </c>
       <c r="L5">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="M5">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="N5">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="O5">
         <v>2.21</v>
@@ -1146,7 +1146,7 @@
         <v>1.59</v>
       </c>
       <c r="R5">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="S5">
         <v>5</v>
@@ -1161,19 +1161,19 @@
         <v>3.1</v>
       </c>
       <c r="W5">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="Z5">
         <v>1.04</v>
       </c>
       <c r="AA5">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AB5">
         <v>1.25</v>
@@ -1182,22 +1182,22 @@
         <v>3.75</v>
       </c>
       <c r="AD5">
+        <v>1.55</v>
+      </c>
+      <c r="AE5">
+        <v>2.25</v>
+      </c>
+      <c r="AF5">
+        <v>1.29</v>
+      </c>
+      <c r="AG5">
+        <v>3.5</v>
+      </c>
+      <c r="AH5">
+        <v>2.3</v>
+      </c>
+      <c r="AI5">
         <v>1.57</v>
-      </c>
-      <c r="AE5">
-        <v>2.15</v>
-      </c>
-      <c r="AF5">
-        <v>1.25</v>
-      </c>
-      <c r="AG5">
-        <v>3.4</v>
-      </c>
-      <c r="AH5">
-        <v>2.33</v>
-      </c>
-      <c r="AI5">
-        <v>1.58</v>
       </c>
       <c r="AJ5" t="s">
         <v>82</v>
@@ -1360,13 +1360,13 @@
         <v>80</v>
       </c>
       <c r="L7">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="M7">
-        <v>2.71</v>
+        <v>2.87</v>
       </c>
       <c r="N7">
-        <v>2.9</v>
+        <v>3.06</v>
       </c>
       <c r="O7">
         <v>1.83</v>
@@ -1381,10 +1381,10 @@
         <v>1.52</v>
       </c>
       <c r="S7">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="T7">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="U7">
         <v>1.27</v>
@@ -1402,7 +1402,7 @@
         <v>6</v>
       </c>
       <c r="Z7">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AA7">
         <v>2.4</v>
@@ -1411,16 +1411,16 @@
         <v>2.5</v>
       </c>
       <c r="AC7">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AD7">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AE7">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AF7">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AG7">
         <v>1.73</v>
@@ -1610,19 +1610,19 @@
         <v>2.4</v>
       </c>
       <c r="R9">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="S9">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="T9">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="U9">
         <v>1.25</v>
       </c>
       <c r="V9">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W9">
         <v>1.04</v>
@@ -1634,25 +1634,25 @@
         <v>5.5</v>
       </c>
       <c r="Z9">
-        <v>1.48</v>
+        <v>1.56</v>
       </c>
       <c r="AA9">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="AB9">
         <v>2.69</v>
       </c>
       <c r="AC9">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AD9">
         <v>5.35</v>
       </c>
       <c r="AE9">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AF9">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AG9">
         <v>1.62</v>
@@ -1661,7 +1661,7 @@
         <v>11.5</v>
       </c>
       <c r="AI9">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AJ9" t="s">
         <v>82</v>
@@ -1708,13 +1708,13 @@
         <v>80</v>
       </c>
       <c r="L10">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="M10">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N10">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="O10">
         <v>1.53</v>
@@ -1732,7 +1732,7 @@
         <v>2.3</v>
       </c>
       <c r="T10">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="U10">
         <v>1.25</v>
@@ -1744,10 +1744,10 @@
         <v>1.03</v>
       </c>
       <c r="X10">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="Z10">
         <v>1.5</v>
@@ -1756,7 +1756,7 @@
         <v>2.4</v>
       </c>
       <c r="AB10">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AC10">
         <v>1.48</v>
@@ -1765,7 +1765,7 @@
         <v>4.75</v>
       </c>
       <c r="AE10">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF10">
         <v>2.25</v>
@@ -1774,7 +1774,7 @@
         <v>1.57</v>
       </c>
       <c r="AH10">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AI10">
         <v>1.02</v>
@@ -1824,13 +1824,13 @@
         <v>80</v>
       </c>
       <c r="L11">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="M11">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="N11">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="O11">
         <v>1.83</v>
@@ -1854,13 +1854,13 @@
         <v>1.33</v>
       </c>
       <c r="V11">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="W11">
         <v>1.06</v>
       </c>
       <c r="X11">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y11">
         <v>7.5</v>
@@ -1890,7 +1890,7 @@
         <v>1.85</v>
       </c>
       <c r="AH11">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AI11">
         <v>1.03</v>
@@ -2172,13 +2172,13 @@
         <v>80</v>
       </c>
       <c r="L14">
-        <v>2.27</v>
+        <v>2.36</v>
       </c>
       <c r="M14">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="N14">
-        <v>3.06</v>
+        <v>3.3</v>
       </c>
       <c r="O14">
         <v>1.83</v>
@@ -2196,7 +2196,7 @@
         <v>2.3</v>
       </c>
       <c r="T14">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="U14">
         <v>1.22</v>
@@ -2214,19 +2214,19 @@
         <v>5.5</v>
       </c>
       <c r="Z14">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
       <c r="AA14">
         <v>2.2</v>
       </c>
       <c r="AB14">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AC14">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AD14">
-        <v>5.7</v>
+        <v>5.75</v>
       </c>
       <c r="AE14">
         <v>1.11</v>
@@ -2238,7 +2238,7 @@
         <v>1.57</v>
       </c>
       <c r="AH14">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AI14">
         <v>1.01</v>

--- a/jogos_2025-07-14.xlsx
+++ b/jogos_2025-07-14.xlsx
@@ -184,12 +184,12 @@
     <t>ÍBV</t>
   </si>
   <si>
+    <t>ÍA</t>
+  </si>
+  <si>
     <t>Afturelding</t>
   </si>
   <si>
-    <t>ÍA</t>
-  </si>
-  <si>
     <t>Deportivo Riestra</t>
   </si>
   <si>
@@ -199,21 +199,21 @@
     <t>Banfield</t>
   </si>
   <si>
+    <t>Maringá</t>
+  </si>
+  <si>
     <t>Retrô</t>
   </si>
   <si>
-    <t>Maringá</t>
-  </si>
-  <si>
     <t>Juventude</t>
   </si>
   <si>
+    <t>Unión Santa Fe</t>
+  </si>
+  <si>
     <t>Vélez Sarsfield</t>
   </si>
   <si>
-    <t>Unión Santa Fe</t>
-  </si>
-  <si>
     <t>Botafogo SP</t>
   </si>
   <si>
@@ -223,12 +223,12 @@
     <t>Stjarnan</t>
   </si>
   <si>
+    <t>KR</t>
+  </si>
+  <si>
     <t>Fram</t>
   </si>
   <si>
-    <t>KR</t>
-  </si>
-  <si>
     <t>Lanús</t>
   </si>
   <si>
@@ -238,19 +238,19 @@
     <t>Defensa y Justicia</t>
   </si>
   <si>
+    <t>Brusque</t>
+  </si>
+  <si>
     <t>CSA</t>
   </si>
   <si>
-    <t>Brusque</t>
-  </si>
-  <si>
     <t>Sport Recife</t>
   </si>
   <si>
+    <t>Estudiantes</t>
+  </si>
+  <si>
     <t>Tigre</t>
-  </si>
-  <si>
-    <t>Estudiantes</t>
   </si>
   <si>
     <t>Volta Redonda</t>
@@ -1009,79 +1009,79 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L4">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="M4">
-        <v>3.51</v>
+        <v>4.33</v>
       </c>
       <c r="N4">
-        <v>2.63</v>
+        <v>1.66</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AJ4" t="s">
         <v>82</v>
@@ -1125,79 +1125,79 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L5">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="M5">
-        <v>4.33</v>
+        <v>3.51</v>
       </c>
       <c r="N5">
-        <v>1.66</v>
+        <v>2.63</v>
       </c>
       <c r="O5">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="P5">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="Q5">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="R5">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="S5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="V5">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="W5">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y5">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="Z5">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AA5">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="AB5">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC5">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AD5">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AE5">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AH5">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AJ5" t="s">
         <v>82</v>
@@ -1592,76 +1592,76 @@
         <v>80</v>
       </c>
       <c r="L9">
-        <v>2.44</v>
+        <v>1.88</v>
       </c>
       <c r="M9">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="N9">
-        <v>3</v>
+        <v>5.2</v>
       </c>
       <c r="O9">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="P9">
-        <v>5.5</v>
+        <v>8.1</v>
       </c>
       <c r="Q9">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="R9">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="S9">
         <v>2.3</v>
       </c>
       <c r="T9">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="U9">
         <v>1.25</v>
       </c>
       <c r="V9">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W9">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X9">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="Y9">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="Z9">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AA9">
+        <v>2.4</v>
+      </c>
+      <c r="AB9">
+        <v>2.3</v>
+      </c>
+      <c r="AC9">
+        <v>1.48</v>
+      </c>
+      <c r="AD9">
+        <v>4.75</v>
+      </c>
+      <c r="AE9">
+        <v>1.14</v>
+      </c>
+      <c r="AF9">
         <v>2.25</v>
       </c>
-      <c r="AB9">
-        <v>2.69</v>
-      </c>
-      <c r="AC9">
-        <v>1.4</v>
-      </c>
-      <c r="AD9">
-        <v>5.35</v>
-      </c>
-      <c r="AE9">
-        <v>1.11</v>
-      </c>
-      <c r="AF9">
-        <v>2.15</v>
-      </c>
       <c r="AG9">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AH9">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AI9">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AJ9" t="s">
         <v>82</v>
@@ -1708,76 +1708,76 @@
         <v>80</v>
       </c>
       <c r="L10">
-        <v>1.88</v>
+        <v>2.44</v>
       </c>
       <c r="M10">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="N10">
-        <v>5.2</v>
+        <v>3</v>
       </c>
       <c r="O10">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="P10">
-        <v>8.1</v>
+        <v>5.5</v>
       </c>
       <c r="Q10">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="R10">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="S10">
         <v>2.3</v>
       </c>
       <c r="T10">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="U10">
         <v>1.25</v>
       </c>
       <c r="V10">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W10">
+        <v>1.04</v>
+      </c>
+      <c r="X10">
+        <v>1.11</v>
+      </c>
+      <c r="Y10">
+        <v>5.5</v>
+      </c>
+      <c r="Z10">
+        <v>1.56</v>
+      </c>
+      <c r="AA10">
+        <v>2.25</v>
+      </c>
+      <c r="AB10">
+        <v>2.69</v>
+      </c>
+      <c r="AC10">
+        <v>1.4</v>
+      </c>
+      <c r="AD10">
+        <v>5.35</v>
+      </c>
+      <c r="AE10">
+        <v>1.11</v>
+      </c>
+      <c r="AF10">
+        <v>2.15</v>
+      </c>
+      <c r="AG10">
+        <v>1.62</v>
+      </c>
+      <c r="AH10">
+        <v>11.5</v>
+      </c>
+      <c r="AI10">
         <v>1.03</v>
-      </c>
-      <c r="X10">
-        <v>1.03</v>
-      </c>
-      <c r="Y10">
-        <v>7.4</v>
-      </c>
-      <c r="Z10">
-        <v>1.5</v>
-      </c>
-      <c r="AA10">
-        <v>2.4</v>
-      </c>
-      <c r="AB10">
-        <v>2.3</v>
-      </c>
-      <c r="AC10">
-        <v>1.48</v>
-      </c>
-      <c r="AD10">
-        <v>4.75</v>
-      </c>
-      <c r="AE10">
-        <v>1.14</v>
-      </c>
-      <c r="AF10">
-        <v>2.25</v>
-      </c>
-      <c r="AG10">
-        <v>1.57</v>
-      </c>
-      <c r="AH10">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AI10">
-        <v>1.02</v>
       </c>
       <c r="AJ10" t="s">
         <v>82</v>
@@ -1940,76 +1940,76 @@
         <v>80</v>
       </c>
       <c r="L12">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="M12">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="N12">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="O12">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="P12">
+        <v>6.5</v>
+      </c>
+      <c r="Q12">
+        <v>2.25</v>
+      </c>
+      <c r="R12">
+        <v>1.53</v>
+      </c>
+      <c r="S12">
+        <v>2.38</v>
+      </c>
+      <c r="T12">
+        <v>3.5</v>
+      </c>
+      <c r="U12">
+        <v>1.29</v>
+      </c>
+      <c r="V12">
+        <v>11</v>
+      </c>
+      <c r="W12">
+        <v>1.05</v>
+      </c>
+      <c r="X12">
+        <v>1.1</v>
+      </c>
+      <c r="Y12">
+        <v>6.5</v>
+      </c>
+      <c r="Z12">
+        <v>1.48</v>
+      </c>
+      <c r="AA12">
+        <v>2.43</v>
+      </c>
+      <c r="AB12">
+        <v>2.5</v>
+      </c>
+      <c r="AC12">
+        <v>1.5</v>
+      </c>
+      <c r="AD12">
         <v>5</v>
       </c>
-      <c r="Q12">
-        <v>2.88</v>
-      </c>
-      <c r="R12">
-        <v>1.67</v>
-      </c>
-      <c r="S12">
-        <v>2.1</v>
-      </c>
-      <c r="T12">
-        <v>4.33</v>
-      </c>
-      <c r="U12">
-        <v>1.2</v>
-      </c>
-      <c r="V12">
-        <v>15</v>
-      </c>
-      <c r="W12">
-        <v>1.03</v>
-      </c>
-      <c r="X12">
-        <v>1.14</v>
-      </c>
-      <c r="Y12">
-        <v>5.5</v>
-      </c>
-      <c r="Z12">
-        <v>1.58</v>
-      </c>
-      <c r="AA12">
-        <v>2.18</v>
-      </c>
-      <c r="AB12">
-        <v>3.1</v>
-      </c>
-      <c r="AC12">
-        <v>1.36</v>
-      </c>
-      <c r="AD12">
-        <v>6.5</v>
-      </c>
       <c r="AE12">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AF12">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AG12">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AH12">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="AI12">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AJ12" t="s">
         <v>82</v>
@@ -2056,76 +2056,76 @@
         <v>80</v>
       </c>
       <c r="L13">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="M13">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="N13">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="O13">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="P13">
+        <v>5</v>
+      </c>
+      <c r="Q13">
+        <v>2.88</v>
+      </c>
+      <c r="R13">
+        <v>1.67</v>
+      </c>
+      <c r="S13">
+        <v>2.1</v>
+      </c>
+      <c r="T13">
+        <v>4.33</v>
+      </c>
+      <c r="U13">
+        <v>1.2</v>
+      </c>
+      <c r="V13">
+        <v>15</v>
+      </c>
+      <c r="W13">
+        <v>1.03</v>
+      </c>
+      <c r="X13">
+        <v>1.14</v>
+      </c>
+      <c r="Y13">
+        <v>5.5</v>
+      </c>
+      <c r="Z13">
+        <v>1.58</v>
+      </c>
+      <c r="AA13">
+        <v>2.18</v>
+      </c>
+      <c r="AB13">
+        <v>3.1</v>
+      </c>
+      <c r="AC13">
+        <v>1.36</v>
+      </c>
+      <c r="AD13">
         <v>6.5</v>
       </c>
-      <c r="Q13">
-        <v>2.25</v>
-      </c>
-      <c r="R13">
-        <v>1.53</v>
-      </c>
-      <c r="S13">
-        <v>2.38</v>
-      </c>
-      <c r="T13">
-        <v>3.5</v>
-      </c>
-      <c r="U13">
-        <v>1.29</v>
-      </c>
-      <c r="V13">
+      <c r="AE13">
+        <v>1.1</v>
+      </c>
+      <c r="AF13">
+        <v>2.5</v>
+      </c>
+      <c r="AG13">
+        <v>1.5</v>
+      </c>
+      <c r="AH13">
         <v>11</v>
       </c>
-      <c r="W13">
-        <v>1.05</v>
-      </c>
-      <c r="X13">
-        <v>1.1</v>
-      </c>
-      <c r="Y13">
-        <v>6.5</v>
-      </c>
-      <c r="Z13">
-        <v>1.48</v>
-      </c>
-      <c r="AA13">
-        <v>2.43</v>
-      </c>
-      <c r="AB13">
-        <v>2.5</v>
-      </c>
-      <c r="AC13">
-        <v>1.5</v>
-      </c>
-      <c r="AD13">
-        <v>5</v>
-      </c>
-      <c r="AE13">
-        <v>1.17</v>
-      </c>
-      <c r="AF13">
-        <v>2</v>
-      </c>
-      <c r="AG13">
-        <v>1.75</v>
-      </c>
-      <c r="AH13">
-        <v>9.5</v>
-      </c>
       <c r="AI13">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AJ13" t="s">
         <v>82</v>

--- a/jogos_2025-07-14.xlsx
+++ b/jogos_2025-07-14.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="80">
   <si>
     <t>Date</t>
   </si>
@@ -187,9 +187,6 @@
     <t>ÍA</t>
   </si>
   <si>
-    <t>Afturelding</t>
-  </si>
-  <si>
     <t>Deportivo Riestra</t>
   </si>
   <si>
@@ -226,9 +223,6 @@
     <t>KR</t>
   </si>
   <si>
-    <t>Fram</t>
-  </si>
-  <si>
     <t>Lanús</t>
   </si>
   <si>
@@ -257,9 +251,6 @@
   </si>
   <si>
     <t>incomplete</t>
-  </si>
-  <si>
-    <t>suspended</t>
   </si>
   <si>
     <t>[]</t>
@@ -626,7 +617,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL14"/>
+  <dimension ref="A1:AL13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:38">
@@ -762,7 +753,7 @@
         <v>54</v>
       </c>
       <c r="F2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -777,7 +768,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L2">
         <v>3.3</v>
@@ -852,10 +843,10 @@
         <v>1.2</v>
       </c>
       <c r="AJ2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AK2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AL2" s="3">
         <v>45852.58333333334</v>
@@ -878,7 +869,7 @@
         <v>55</v>
       </c>
       <c r="F3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -893,16 +884,16 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L3">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="M3">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N3">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="O3">
         <v>1.98</v>
@@ -914,13 +905,13 @@
         <v>1.88</v>
       </c>
       <c r="R3">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S3">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="T3">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="U3">
         <v>1.57</v>
@@ -929,13 +920,13 @@
         <v>5</v>
       </c>
       <c r="W3">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X3">
         <v>1.03</v>
       </c>
       <c r="Y3">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="Z3">
         <v>1.14</v>
@@ -944,34 +935,34 @@
         <v>4.75</v>
       </c>
       <c r="AB3">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AC3">
         <v>2.25</v>
       </c>
       <c r="AD3">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="AE3">
         <v>1.53</v>
       </c>
       <c r="AF3">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AG3">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AH3">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="AI3">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AJ3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AK3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AL3" s="3">
         <v>45852.64583333334</v>
@@ -994,7 +985,7 @@
         <v>56</v>
       </c>
       <c r="F4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1009,16 +1000,16 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L4">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="M4">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="N4">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="O4">
         <v>2.21</v>
@@ -1033,22 +1024,22 @@
         <v>1.14</v>
       </c>
       <c r="S4">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="T4">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U4">
         <v>2.05</v>
       </c>
       <c r="V4">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="W4">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="X4">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y4">
         <v>36</v>
@@ -1057,37 +1048,37 @@
         <v>1.04</v>
       </c>
       <c r="AA4">
-        <v>8.5</v>
+        <v>9.4</v>
       </c>
       <c r="AB4">
+        <v>1.23</v>
+      </c>
+      <c r="AC4">
+        <v>3.73</v>
+      </c>
+      <c r="AD4">
+        <v>1.57</v>
+      </c>
+      <c r="AE4">
+        <v>2.15</v>
+      </c>
+      <c r="AF4">
         <v>1.25</v>
-      </c>
-      <c r="AC4">
-        <v>3.75</v>
-      </c>
-      <c r="AD4">
-        <v>1.55</v>
-      </c>
-      <c r="AE4">
-        <v>2.25</v>
-      </c>
-      <c r="AF4">
-        <v>1.29</v>
       </c>
       <c r="AG4">
         <v>3.5</v>
       </c>
       <c r="AH4">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AI4">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AJ4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AK4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AL4" s="3">
         <v>45852.67708333334</v>
@@ -1098,10 +1089,10 @@
         <v>45852</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D5" t="s">
         <v>53</v>
@@ -1110,7 +1101,7 @@
         <v>57</v>
       </c>
       <c r="F5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1125,88 +1116,88 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="L5">
-        <v>2.4</v>
+        <v>3.25</v>
       </c>
       <c r="M5">
-        <v>3.51</v>
+        <v>2.75</v>
       </c>
       <c r="N5">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AK5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AL5" s="3">
-        <v>45852.67708333334</v>
+        <v>45852.6875</v>
       </c>
     </row>
     <row r="6" spans="1:38">
@@ -1214,10 +1205,10 @@
         <v>45852</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s">
         <v>53</v>
@@ -1226,7 +1217,7 @@
         <v>58</v>
       </c>
       <c r="F6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1241,88 +1232,88 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L6">
-        <v>3.25</v>
+        <v>2.46</v>
       </c>
       <c r="M6">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="N6">
+        <v>2.9</v>
+      </c>
+      <c r="O6">
+        <v>1.83</v>
+      </c>
+      <c r="P6">
+        <v>6.25</v>
+      </c>
+      <c r="Q6">
+        <v>2.4</v>
+      </c>
+      <c r="R6">
+        <v>1.53</v>
+      </c>
+      <c r="S6">
+        <v>2.45</v>
+      </c>
+      <c r="T6">
+        <v>3.5</v>
+      </c>
+      <c r="U6">
+        <v>1.29</v>
+      </c>
+      <c r="V6">
+        <v>8.6</v>
+      </c>
+      <c r="W6">
+        <v>1.05</v>
+      </c>
+      <c r="X6">
+        <v>1.06</v>
+      </c>
+      <c r="Y6">
+        <v>6.5</v>
+      </c>
+      <c r="Z6">
+        <v>1.48</v>
+      </c>
+      <c r="AA6">
+        <v>2.4</v>
+      </c>
+      <c r="AB6">
         <v>2.5</v>
       </c>
-      <c r="O6">
-        <v>2.5</v>
-      </c>
-      <c r="P6">
+      <c r="AC6">
+        <v>1.5</v>
+      </c>
+      <c r="AD6">
         <v>5</v>
       </c>
-      <c r="Q6">
-        <v>1.91</v>
-      </c>
-      <c r="R6">
-        <v>1.67</v>
-      </c>
-      <c r="S6">
+      <c r="AE6">
+        <v>1.16</v>
+      </c>
+      <c r="AF6">
         <v>2.1</v>
       </c>
-      <c r="T6">
-        <v>4.33</v>
-      </c>
-      <c r="U6">
-        <v>1.2</v>
-      </c>
-      <c r="V6">
-        <v>15</v>
-      </c>
-      <c r="W6">
-        <v>1.03</v>
-      </c>
-      <c r="X6">
-        <v>1.15</v>
-      </c>
-      <c r="Y6">
-        <v>5.25</v>
-      </c>
-      <c r="Z6">
-        <v>1.63</v>
-      </c>
-      <c r="AA6">
-        <v>2.1</v>
-      </c>
-      <c r="AB6">
-        <v>3.1</v>
-      </c>
-      <c r="AC6">
-        <v>1.36</v>
-      </c>
-      <c r="AD6">
-        <v>6.5</v>
-      </c>
-      <c r="AE6">
-        <v>1.1</v>
-      </c>
-      <c r="AF6">
-        <v>2.38</v>
-      </c>
       <c r="AG6">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AH6">
         <v>11</v>
       </c>
       <c r="AI6">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AJ6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AK6" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AL6" s="3">
-        <v>45852.6875</v>
+        <v>45852.79166666666</v>
       </c>
     </row>
     <row r="7" spans="1:38">
@@ -1333,7 +1324,7 @@
         <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D7" t="s">
         <v>53</v>
@@ -1342,7 +1333,7 @@
         <v>59</v>
       </c>
       <c r="F7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1357,85 +1348,85 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L7">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="M7">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="N7">
-        <v>3.06</v>
+        <v>3.4</v>
       </c>
       <c r="O7">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="P7">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="Q7">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R7">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S7">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="T7">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U7">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="V7">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="W7">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="X7">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Y7">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Z7">
         <v>1.5</v>
       </c>
       <c r="AA7">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AB7">
         <v>2.5</v>
       </c>
       <c r="AC7">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="AD7">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AE7">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF7">
         <v>2.05</v>
       </c>
       <c r="AG7">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AH7">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="AI7">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AJ7" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AK7" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AL7" s="3">
         <v>45852.79166666666</v>
@@ -1446,10 +1437,10 @@
         <v>45852</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D8" t="s">
         <v>53</v>
@@ -1458,7 +1449,7 @@
         <v>60</v>
       </c>
       <c r="F8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1473,88 +1464,88 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L8">
-        <v>2.35</v>
+        <v>1.68</v>
       </c>
       <c r="M8">
-        <v>2.9</v>
+        <v>3.26</v>
       </c>
       <c r="N8">
-        <v>3.4</v>
+        <v>5.1</v>
       </c>
       <c r="O8">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="P8">
-        <v>6.5</v>
+        <v>8.1</v>
       </c>
       <c r="Q8">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="R8">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="S8">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="T8">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U8">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="V8">
-        <v>11</v>
+        <v>8.9</v>
       </c>
       <c r="W8">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X8">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="Y8">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="Z8">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="AA8">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="AB8">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="AC8">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AD8">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="AE8">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF8">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AG8">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AH8">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AI8">
         <v>1.05</v>
       </c>
       <c r="AJ8" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AK8" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AL8" s="3">
-        <v>45852.79166666666</v>
+        <v>45852.8125</v>
       </c>
     </row>
     <row r="9" spans="1:38">
@@ -1574,7 +1565,7 @@
         <v>61</v>
       </c>
       <c r="F9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1589,85 +1580,85 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L9">
-        <v>1.88</v>
+        <v>2.46</v>
       </c>
       <c r="M9">
-        <v>3.25</v>
+        <v>2.76</v>
       </c>
       <c r="N9">
-        <v>5.2</v>
+        <v>3.03</v>
       </c>
       <c r="O9">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="P9">
-        <v>8.1</v>
+        <v>5.5</v>
       </c>
       <c r="Q9">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="R9">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="S9">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="T9">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="U9">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="V9">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="W9">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X9">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="Y9">
-        <v>7.4</v>
+        <v>5.4</v>
       </c>
       <c r="Z9">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AA9">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="AB9">
-        <v>2.3</v>
+        <v>2.69</v>
       </c>
       <c r="AC9">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="AD9">
-        <v>4.75</v>
+        <v>5.35</v>
       </c>
       <c r="AE9">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF9">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AG9">
         <v>1.57</v>
       </c>
       <c r="AH9">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="AI9">
         <v>1.02</v>
       </c>
       <c r="AJ9" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AK9" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AL9" s="3">
         <v>45852.8125</v>
@@ -1678,10 +1669,10 @@
         <v>45852</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D10" t="s">
         <v>53</v>
@@ -1690,7 +1681,7 @@
         <v>62</v>
       </c>
       <c r="F10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1705,88 +1696,88 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L10">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="M10">
-        <v>2.7</v>
+        <v>2.85</v>
       </c>
       <c r="N10">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="O10">
         <v>1.83</v>
       </c>
       <c r="P10">
-        <v>5.5</v>
+        <v>7.25</v>
       </c>
       <c r="Q10">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="R10">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="S10">
-        <v>2.3</v>
+        <v>2.66</v>
       </c>
       <c r="T10">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="U10">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="V10">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="W10">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X10">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Y10">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="Z10">
-        <v>1.56</v>
+        <v>1.37</v>
       </c>
       <c r="AA10">
+        <v>2.75</v>
+      </c>
+      <c r="AB10">
         <v>2.25</v>
       </c>
-      <c r="AB10">
-        <v>2.69</v>
-      </c>
       <c r="AC10">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="AD10">
-        <v>5.35</v>
+        <v>4</v>
       </c>
       <c r="AE10">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="AF10">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AG10">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AH10">
-        <v>11.5</v>
+        <v>8</v>
       </c>
       <c r="AI10">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AJ10" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AK10" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AL10" s="3">
-        <v>45852.8125</v>
+        <v>45852.83333333334</v>
       </c>
     </row>
     <row r="11" spans="1:38">
@@ -1794,10 +1785,10 @@
         <v>45852</v>
       </c>
       <c r="B11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s">
         <v>53</v>
@@ -1806,7 +1797,7 @@
         <v>63</v>
       </c>
       <c r="F11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1821,88 +1812,88 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L11">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="M11">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="N11">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="O11">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="P11">
-        <v>7.25</v>
+        <v>6.5</v>
       </c>
       <c r="Q11">
         <v>2.25</v>
       </c>
       <c r="R11">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="S11">
-        <v>2.63</v>
+        <v>2.38</v>
       </c>
       <c r="T11">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="U11">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="V11">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X11">
+        <v>1.1</v>
+      </c>
+      <c r="Y11">
+        <v>6.5</v>
+      </c>
+      <c r="Z11">
+        <v>1.48</v>
+      </c>
+      <c r="AA11">
+        <v>2.43</v>
+      </c>
+      <c r="AB11">
+        <v>2.5</v>
+      </c>
+      <c r="AC11">
+        <v>1.5</v>
+      </c>
+      <c r="AD11">
+        <v>5</v>
+      </c>
+      <c r="AE11">
+        <v>1.17</v>
+      </c>
+      <c r="AF11">
+        <v>2</v>
+      </c>
+      <c r="AG11">
+        <v>1.75</v>
+      </c>
+      <c r="AH11">
+        <v>9.5</v>
+      </c>
+      <c r="AI11">
         <v>1.05</v>
       </c>
-      <c r="Y11">
-        <v>7.5</v>
-      </c>
-      <c r="Z11">
-        <v>1.4</v>
-      </c>
-      <c r="AA11">
-        <v>2.7</v>
-      </c>
-      <c r="AB11">
-        <v>2.25</v>
-      </c>
-      <c r="AC11">
-        <v>1.62</v>
-      </c>
-      <c r="AD11">
-        <v>4.2</v>
-      </c>
-      <c r="AE11">
-        <v>1.2</v>
-      </c>
-      <c r="AF11">
-        <v>1.85</v>
-      </c>
-      <c r="AG11">
-        <v>1.85</v>
-      </c>
-      <c r="AH11">
-        <v>8.5</v>
-      </c>
-      <c r="AI11">
-        <v>1.03</v>
-      </c>
       <c r="AJ11" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AK11" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AL11" s="3">
-        <v>45852.83333333334</v>
+        <v>45852.88541666666</v>
       </c>
     </row>
     <row r="12" spans="1:38">
@@ -1922,7 +1913,7 @@
         <v>64</v>
       </c>
       <c r="F12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1937,85 +1928,85 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="L12">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="M12">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="N12">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="O12">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="P12">
+        <v>5</v>
+      </c>
+      <c r="Q12">
+        <v>2.88</v>
+      </c>
+      <c r="R12">
+        <v>1.67</v>
+      </c>
+      <c r="S12">
+        <v>2.1</v>
+      </c>
+      <c r="T12">
+        <v>4.33</v>
+      </c>
+      <c r="U12">
+        <v>1.2</v>
+      </c>
+      <c r="V12">
+        <v>15</v>
+      </c>
+      <c r="W12">
+        <v>1.03</v>
+      </c>
+      <c r="X12">
+        <v>1.14</v>
+      </c>
+      <c r="Y12">
+        <v>5.5</v>
+      </c>
+      <c r="Z12">
+        <v>1.58</v>
+      </c>
+      <c r="AA12">
+        <v>2.18</v>
+      </c>
+      <c r="AB12">
+        <v>3.1</v>
+      </c>
+      <c r="AC12">
+        <v>1.36</v>
+      </c>
+      <c r="AD12">
         <v>6.5</v>
       </c>
-      <c r="Q12">
-        <v>2.25</v>
-      </c>
-      <c r="R12">
-        <v>1.53</v>
-      </c>
-      <c r="S12">
-        <v>2.38</v>
-      </c>
-      <c r="T12">
-        <v>3.5</v>
-      </c>
-      <c r="U12">
-        <v>1.29</v>
-      </c>
-      <c r="V12">
+      <c r="AE12">
+        <v>1.1</v>
+      </c>
+      <c r="AF12">
+        <v>2.5</v>
+      </c>
+      <c r="AG12">
+        <v>1.5</v>
+      </c>
+      <c r="AH12">
         <v>11</v>
       </c>
-      <c r="W12">
-        <v>1.05</v>
-      </c>
-      <c r="X12">
-        <v>1.1</v>
-      </c>
-      <c r="Y12">
-        <v>6.5</v>
-      </c>
-      <c r="Z12">
-        <v>1.48</v>
-      </c>
-      <c r="AA12">
-        <v>2.43</v>
-      </c>
-      <c r="AB12">
-        <v>2.5</v>
-      </c>
-      <c r="AC12">
-        <v>1.5</v>
-      </c>
-      <c r="AD12">
-        <v>5</v>
-      </c>
-      <c r="AE12">
-        <v>1.17</v>
-      </c>
-      <c r="AF12">
-        <v>2</v>
-      </c>
-      <c r="AG12">
-        <v>1.75</v>
-      </c>
-      <c r="AH12">
-        <v>9.5</v>
-      </c>
       <c r="AI12">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AJ12" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AK12" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AL12" s="3">
         <v>45852.88541666666</v>
@@ -2026,10 +2017,10 @@
         <v>45852</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
         <v>53</v>
@@ -2038,70 +2029,70 @@
         <v>65</v>
       </c>
       <c r="F13" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13" t="s">
         <v>78</v>
       </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13" t="s">
-        <v>80</v>
-      </c>
       <c r="L13">
+        <v>2.27</v>
+      </c>
+      <c r="M13">
+        <v>2.84</v>
+      </c>
+      <c r="N13">
+        <v>3.06</v>
+      </c>
+      <c r="O13">
+        <v>1.83</v>
+      </c>
+      <c r="P13">
+        <v>5.5</v>
+      </c>
+      <c r="Q13">
+        <v>2.5</v>
+      </c>
+      <c r="R13">
+        <v>1.57</v>
+      </c>
+      <c r="S13">
+        <v>2.3</v>
+      </c>
+      <c r="T13">
+        <v>4</v>
+      </c>
+      <c r="U13">
+        <v>1.22</v>
+      </c>
+      <c r="V13">
+        <v>13</v>
+      </c>
+      <c r="W13">
+        <v>1.04</v>
+      </c>
+      <c r="X13">
+        <v>1.13</v>
+      </c>
+      <c r="Y13">
+        <v>5.7</v>
+      </c>
+      <c r="Z13">
+        <v>1.55</v>
+      </c>
+      <c r="AA13">
         <v>2.2</v>
-      </c>
-      <c r="M13">
-        <v>2.8</v>
-      </c>
-      <c r="N13">
-        <v>4.1</v>
-      </c>
-      <c r="O13">
-        <v>1.73</v>
-      </c>
-      <c r="P13">
-        <v>5</v>
-      </c>
-      <c r="Q13">
-        <v>2.88</v>
-      </c>
-      <c r="R13">
-        <v>1.67</v>
-      </c>
-      <c r="S13">
-        <v>2.1</v>
-      </c>
-      <c r="T13">
-        <v>4.33</v>
-      </c>
-      <c r="U13">
-        <v>1.2</v>
-      </c>
-      <c r="V13">
-        <v>15</v>
-      </c>
-      <c r="W13">
-        <v>1.03</v>
-      </c>
-      <c r="X13">
-        <v>1.14</v>
-      </c>
-      <c r="Y13">
-        <v>5.5</v>
-      </c>
-      <c r="Z13">
-        <v>1.58</v>
-      </c>
-      <c r="AA13">
-        <v>2.18</v>
       </c>
       <c r="AB13">
         <v>3.1</v>
@@ -2110,146 +2101,30 @@
         <v>1.36</v>
       </c>
       <c r="AD13">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="AE13">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AF13">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AG13">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AH13">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AI13">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AJ13" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AK13" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="AL13" s="3">
-        <v>45852.88541666666</v>
-      </c>
-    </row>
-    <row r="14" spans="1:38">
-      <c r="A14" s="2">
-        <v>45852</v>
-      </c>
-      <c r="B14" t="s">
-        <v>46</v>
-      </c>
-      <c r="C14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" t="s">
-        <v>53</v>
-      </c>
-      <c r="E14" t="s">
-        <v>66</v>
-      </c>
-      <c r="F14" t="s">
-        <v>79</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14" t="s">
-        <v>80</v>
-      </c>
-      <c r="L14">
-        <v>2.36</v>
-      </c>
-      <c r="M14">
-        <v>3.1</v>
-      </c>
-      <c r="N14">
-        <v>3.3</v>
-      </c>
-      <c r="O14">
-        <v>1.83</v>
-      </c>
-      <c r="P14">
-        <v>5.5</v>
-      </c>
-      <c r="Q14">
-        <v>2.5</v>
-      </c>
-      <c r="R14">
-        <v>1.57</v>
-      </c>
-      <c r="S14">
-        <v>2.3</v>
-      </c>
-      <c r="T14">
-        <v>3.9</v>
-      </c>
-      <c r="U14">
-        <v>1.22</v>
-      </c>
-      <c r="V14">
-        <v>13.5</v>
-      </c>
-      <c r="W14">
-        <v>1.04</v>
-      </c>
-      <c r="X14">
-        <v>1.12</v>
-      </c>
-      <c r="Y14">
-        <v>5.5</v>
-      </c>
-      <c r="Z14">
-        <v>1.65</v>
-      </c>
-      <c r="AA14">
-        <v>2.2</v>
-      </c>
-      <c r="AB14">
-        <v>3</v>
-      </c>
-      <c r="AC14">
-        <v>1.34</v>
-      </c>
-      <c r="AD14">
-        <v>5.75</v>
-      </c>
-      <c r="AE14">
-        <v>1.11</v>
-      </c>
-      <c r="AF14">
-        <v>2.3</v>
-      </c>
-      <c r="AG14">
-        <v>1.57</v>
-      </c>
-      <c r="AH14">
-        <v>11</v>
-      </c>
-      <c r="AI14">
-        <v>1.01</v>
-      </c>
-      <c r="AJ14" t="s">
-        <v>82</v>
-      </c>
-      <c r="AK14" t="s">
-        <v>82</v>
-      </c>
-      <c r="AL14" s="3">
         <v>45852.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-07-14.xlsx
+++ b/jogos_2025-07-14.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="80">
   <si>
     <t>Date</t>
   </si>
@@ -190,18 +190,18 @@
     <t>Deportivo Riestra</t>
   </si>
   <si>
+    <t>Banfield</t>
+  </si>
+  <si>
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>Banfield</t>
+    <t>Retrô</t>
   </si>
   <si>
     <t>Maringá</t>
   </si>
   <si>
-    <t>Retrô</t>
-  </si>
-  <si>
     <t>Juventude</t>
   </si>
   <si>
@@ -226,16 +226,16 @@
     <t>Lanús</t>
   </si>
   <si>
+    <t>Defensa y Justicia</t>
+  </si>
+  <si>
     <t>Avaí</t>
   </si>
   <si>
-    <t>Defensa y Justicia</t>
+    <t>CSA</t>
   </si>
   <si>
     <t>Brusque</t>
-  </si>
-  <si>
-    <t>CSA</t>
   </si>
   <si>
     <t>Sport Recife</t>
@@ -617,7 +617,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL13"/>
+  <dimension ref="A1:AL16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:38">
@@ -887,13 +887,13 @@
         <v>78</v>
       </c>
       <c r="L3">
-        <v>2.98</v>
+        <v>2.75</v>
       </c>
       <c r="M3">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="N3">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="O3">
         <v>1.98</v>
@@ -908,16 +908,16 @@
         <v>1.25</v>
       </c>
       <c r="S3">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="T3">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="U3">
         <v>1.57</v>
       </c>
       <c r="V3">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="W3">
         <v>1.13</v>
@@ -929,19 +929,19 @@
         <v>15</v>
       </c>
       <c r="Z3">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AA3">
         <v>4.75</v>
       </c>
       <c r="AB3">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AC3">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AD3">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="AE3">
         <v>1.53</v>
@@ -950,13 +950,13 @@
         <v>1.51</v>
       </c>
       <c r="AG3">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="AH3">
         <v>4</v>
       </c>
       <c r="AI3">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AJ3" t="s">
         <v>79</v>
@@ -1003,13 +1003,13 @@
         <v>78</v>
       </c>
       <c r="L4">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="M4">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="N4">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="O4">
         <v>2.21</v>
@@ -1024,7 +1024,7 @@
         <v>1.14</v>
       </c>
       <c r="S4">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="T4">
         <v>1.73</v>
@@ -1033,10 +1033,10 @@
         <v>2.05</v>
       </c>
       <c r="V4">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="W4">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="X4">
         <v>1</v>
@@ -1045,25 +1045,25 @@
         <v>36</v>
       </c>
       <c r="Z4">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AA4">
-        <v>9.4</v>
+        <v>8.5</v>
       </c>
       <c r="AB4">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AC4">
-        <v>3.73</v>
+        <v>3.9</v>
       </c>
       <c r="AD4">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="AE4">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AF4">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AG4">
         <v>3.5</v>
@@ -1072,7 +1072,7 @@
         <v>2.25</v>
       </c>
       <c r="AI4">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="AJ4" t="s">
         <v>79</v>
@@ -1208,7 +1208,7 @@
         <v>42</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D6" t="s">
         <v>53</v>
@@ -1235,76 +1235,76 @@
         <v>78</v>
       </c>
       <c r="L6">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="M6">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="N6">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O6">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P6">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="Q6">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="R6">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S6">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V6">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="W6">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X6">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y6">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Z6">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA6">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB6">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC6">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD6">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE6">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AF6">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH6">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AI6">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="s">
         <v>79</v>
@@ -1330,10 +1330,10 @@
         <v>53</v>
       </c>
       <c r="E7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1437,19 +1437,19 @@
         <v>45852</v>
       </c>
       <c r="B8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D8" t="s">
         <v>53</v>
       </c>
       <c r="E8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1467,73 +1467,73 @@
         <v>78</v>
       </c>
       <c r="L8">
-        <v>1.68</v>
+        <v>2.28</v>
       </c>
       <c r="M8">
-        <v>3.26</v>
+        <v>2.9</v>
       </c>
       <c r="N8">
-        <v>5.1</v>
+        <v>3.15</v>
       </c>
       <c r="O8">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="P8">
-        <v>8.1</v>
+        <v>6.25</v>
       </c>
       <c r="Q8">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="R8">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="S8">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="T8">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="U8">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="V8">
-        <v>8.9</v>
+        <v>8.5</v>
       </c>
       <c r="W8">
+        <v>1.05</v>
+      </c>
+      <c r="X8">
         <v>1.06</v>
-      </c>
-      <c r="X8">
-        <v>1.03</v>
       </c>
       <c r="Y8">
         <v>6</v>
       </c>
       <c r="Z8">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="AA8">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="AB8">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="AC8">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AD8">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AE8">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF8">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AG8">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AH8">
-        <v>9.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="AI8">
         <v>1.05</v>
@@ -1545,7 +1545,7 @@
         <v>79</v>
       </c>
       <c r="AL8" s="3">
-        <v>45852.8125</v>
+        <v>45852.79166666666</v>
       </c>
     </row>
     <row r="9" spans="1:38">
@@ -1562,10 +1562,10 @@
         <v>53</v>
       </c>
       <c r="E9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1604,10 +1604,10 @@
         <v>1.6</v>
       </c>
       <c r="S9">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="T9">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="U9">
         <v>1.22</v>
@@ -1622,37 +1622,37 @@
         <v>1.12</v>
       </c>
       <c r="Y9">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Z9">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AA9">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="AB9">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AC9">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AD9">
         <v>5.35</v>
       </c>
       <c r="AE9">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF9">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AG9">
         <v>1.57</v>
       </c>
       <c r="AH9">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AI9">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AJ9" t="s">
         <v>79</v>
@@ -1669,19 +1669,19 @@
         <v>45852</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D10" t="s">
         <v>53</v>
       </c>
       <c r="E10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1699,76 +1699,76 @@
         <v>78</v>
       </c>
       <c r="L10">
-        <v>2.32</v>
+        <v>1.68</v>
       </c>
       <c r="M10">
-        <v>2.85</v>
+        <v>3.24</v>
       </c>
       <c r="N10">
-        <v>2.95</v>
+        <v>4.88</v>
       </c>
       <c r="O10">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="P10">
-        <v>7.25</v>
+        <v>8.1</v>
       </c>
       <c r="Q10">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="R10">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="S10">
-        <v>2.66</v>
+        <v>2.48</v>
       </c>
       <c r="T10">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="U10">
         <v>1.3</v>
       </c>
       <c r="V10">
-        <v>8.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="W10">
         <v>1.06</v>
       </c>
       <c r="X10">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z10">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AA10">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="AB10">
-        <v>2.25</v>
+        <v>2.32</v>
       </c>
       <c r="AC10">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="AD10">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AE10">
         <v>1.18</v>
       </c>
       <c r="AF10">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="AG10">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AH10">
-        <v>8</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="AI10">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AJ10" t="s">
         <v>79</v>
@@ -1777,7 +1777,7 @@
         <v>79</v>
       </c>
       <c r="AL10" s="3">
-        <v>45852.83333333334</v>
+        <v>45852.8125</v>
       </c>
     </row>
     <row r="11" spans="1:38">
@@ -1785,19 +1785,19 @@
         <v>45852</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
         <v>53</v>
       </c>
       <c r="E11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1815,76 +1815,76 @@
         <v>78</v>
       </c>
       <c r="L11">
-        <v>2.63</v>
+        <v>2.24</v>
       </c>
       <c r="M11">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="N11">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O11">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="P11">
-        <v>6.5</v>
+        <v>7.25</v>
       </c>
       <c r="Q11">
         <v>2.25</v>
       </c>
       <c r="R11">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="S11">
-        <v>2.38</v>
+        <v>2.66</v>
       </c>
       <c r="T11">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="U11">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="V11">
-        <v>11</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W11">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="Y11">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="Z11">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="AA11">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="AB11">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AC11">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AD11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE11">
         <v>1.17</v>
       </c>
       <c r="AF11">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG11">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AH11">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="AI11">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AJ11" t="s">
         <v>79</v>
@@ -1893,7 +1893,7 @@
         <v>79</v>
       </c>
       <c r="AL11" s="3">
-        <v>45852.88541666666</v>
+        <v>45852.83333333334</v>
       </c>
     </row>
     <row r="12" spans="1:38">
@@ -1910,10 +1910,10 @@
         <v>53</v>
       </c>
       <c r="E12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F12" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1931,76 +1931,76 @@
         <v>78</v>
       </c>
       <c r="L12">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="M12">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="N12">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O12">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="P12">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q12">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R12">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T12">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V12">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="W12">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X12">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Y12">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="Z12">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AA12">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AC12">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD12">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AE12">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF12">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AG12">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AH12">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AI12">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="s">
         <v>79</v>
@@ -2017,19 +2017,19 @@
         <v>45852</v>
       </c>
       <c r="B13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D13" t="s">
         <v>53</v>
       </c>
       <c r="E13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F13" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2047,52 +2047,52 @@
         <v>78</v>
       </c>
       <c r="L13">
-        <v>2.27</v>
+        <v>2.2</v>
       </c>
       <c r="M13">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="N13">
-        <v>3.06</v>
+        <v>4.1</v>
       </c>
       <c r="O13">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="P13">
+        <v>5</v>
+      </c>
+      <c r="Q13">
+        <v>2.88</v>
+      </c>
+      <c r="R13">
+        <v>1.67</v>
+      </c>
+      <c r="S13">
+        <v>2.1</v>
+      </c>
+      <c r="T13">
+        <v>4.33</v>
+      </c>
+      <c r="U13">
+        <v>1.2</v>
+      </c>
+      <c r="V13">
+        <v>15</v>
+      </c>
+      <c r="W13">
+        <v>1.03</v>
+      </c>
+      <c r="X13">
+        <v>1.14</v>
+      </c>
+      <c r="Y13">
         <v>5.5</v>
       </c>
-      <c r="Q13">
-        <v>2.5</v>
-      </c>
-      <c r="R13">
-        <v>1.57</v>
-      </c>
-      <c r="S13">
-        <v>2.3</v>
-      </c>
-      <c r="T13">
-        <v>4</v>
-      </c>
-      <c r="U13">
-        <v>1.22</v>
-      </c>
-      <c r="V13">
-        <v>13</v>
-      </c>
-      <c r="W13">
-        <v>1.04</v>
-      </c>
-      <c r="X13">
-        <v>1.13</v>
-      </c>
-      <c r="Y13">
-        <v>5.7</v>
-      </c>
       <c r="Z13">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AA13">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AB13">
         <v>3.1</v>
@@ -2101,30 +2101,378 @@
         <v>1.36</v>
       </c>
       <c r="AD13">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="AE13">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF13">
+        <v>2.5</v>
+      </c>
+      <c r="AG13">
+        <v>1.5</v>
+      </c>
+      <c r="AH13">
+        <v>11</v>
+      </c>
+      <c r="AI13">
+        <v>1.03</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>79</v>
+      </c>
+      <c r="AK13" t="s">
+        <v>79</v>
+      </c>
+      <c r="AL13" s="3">
+        <v>45852.88541666666</v>
+      </c>
+    </row>
+    <row r="14" spans="1:38">
+      <c r="A14" s="2">
+        <v>45852</v>
+      </c>
+      <c r="B14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" t="s">
+        <v>64</v>
+      </c>
+      <c r="F14" t="s">
+        <v>76</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14" t="s">
+        <v>78</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>79</v>
+      </c>
+      <c r="AK14" t="s">
+        <v>79</v>
+      </c>
+      <c r="AL14" s="3">
+        <v>45852.88541666666</v>
+      </c>
+    </row>
+    <row r="15" spans="1:38">
+      <c r="A15" s="2">
+        <v>45852</v>
+      </c>
+      <c r="B15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" t="s">
+        <v>63</v>
+      </c>
+      <c r="F15" t="s">
+        <v>75</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15" t="s">
+        <v>78</v>
+      </c>
+      <c r="L15">
+        <v>2.63</v>
+      </c>
+      <c r="M15">
+        <v>2.9</v>
+      </c>
+      <c r="N15">
+        <v>3</v>
+      </c>
+      <c r="O15">
+        <v>1.91</v>
+      </c>
+      <c r="P15">
+        <v>6.5</v>
+      </c>
+      <c r="Q15">
+        <v>2.25</v>
+      </c>
+      <c r="R15">
+        <v>1.53</v>
+      </c>
+      <c r="S15">
+        <v>2.38</v>
+      </c>
+      <c r="T15">
+        <v>3.5</v>
+      </c>
+      <c r="U15">
+        <v>1.29</v>
+      </c>
+      <c r="V15">
+        <v>11</v>
+      </c>
+      <c r="W15">
+        <v>1.05</v>
+      </c>
+      <c r="X15">
+        <v>1.1</v>
+      </c>
+      <c r="Y15">
+        <v>6.5</v>
+      </c>
+      <c r="Z15">
+        <v>1.48</v>
+      </c>
+      <c r="AA15">
+        <v>2.43</v>
+      </c>
+      <c r="AB15">
+        <v>2.5</v>
+      </c>
+      <c r="AC15">
+        <v>1.5</v>
+      </c>
+      <c r="AD15">
+        <v>5</v>
+      </c>
+      <c r="AE15">
+        <v>1.17</v>
+      </c>
+      <c r="AF15">
+        <v>2</v>
+      </c>
+      <c r="AG15">
+        <v>1.75</v>
+      </c>
+      <c r="AH15">
+        <v>9.5</v>
+      </c>
+      <c r="AI15">
+        <v>1.05</v>
+      </c>
+      <c r="AJ15" t="s">
+        <v>79</v>
+      </c>
+      <c r="AK15" t="s">
+        <v>79</v>
+      </c>
+      <c r="AL15" s="3">
+        <v>45852.88541666666</v>
+      </c>
+    </row>
+    <row r="16" spans="1:38">
+      <c r="A16" s="2">
+        <v>45852</v>
+      </c>
+      <c r="B16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" t="s">
+        <v>65</v>
+      </c>
+      <c r="F16" t="s">
+        <v>77</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16" t="s">
+        <v>78</v>
+      </c>
+      <c r="L16">
+        <v>2.23</v>
+      </c>
+      <c r="M16">
+        <v>2.83</v>
+      </c>
+      <c r="N16">
+        <v>3.38</v>
+      </c>
+      <c r="O16">
+        <v>1.83</v>
+      </c>
+      <c r="P16">
+        <v>5.5</v>
+      </c>
+      <c r="Q16">
+        <v>2.5</v>
+      </c>
+      <c r="R16">
+        <v>1.62</v>
+      </c>
+      <c r="S16">
+        <v>2.2</v>
+      </c>
+      <c r="T16">
+        <v>4</v>
+      </c>
+      <c r="U16">
+        <v>1.22</v>
+      </c>
+      <c r="V16">
+        <v>13</v>
+      </c>
+      <c r="W16">
+        <v>1.03</v>
+      </c>
+      <c r="X16">
+        <v>1.13</v>
+      </c>
+      <c r="Y16">
+        <v>5.8</v>
+      </c>
+      <c r="Z16">
+        <v>1.62</v>
+      </c>
+      <c r="AA16">
+        <v>2.2</v>
+      </c>
+      <c r="AB16">
+        <v>2.8</v>
+      </c>
+      <c r="AC16">
+        <v>1.38</v>
+      </c>
+      <c r="AD16">
+        <v>5.8</v>
+      </c>
+      <c r="AE16">
+        <v>1.08</v>
+      </c>
+      <c r="AF16">
         <v>2.3</v>
       </c>
-      <c r="AG13">
+      <c r="AG16">
         <v>1.57</v>
       </c>
-      <c r="AH13">
+      <c r="AH16">
         <v>12.5</v>
       </c>
-      <c r="AI13">
+      <c r="AI16">
         <v>1.01</v>
       </c>
-      <c r="AJ13" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK13" t="s">
-        <v>79</v>
-      </c>
-      <c r="AL13" s="3">
+      <c r="AJ16" t="s">
+        <v>79</v>
+      </c>
+      <c r="AK16" t="s">
+        <v>79</v>
+      </c>
+      <c r="AL16" s="3">
         <v>45852.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-07-14.xlsx
+++ b/jogos_2025-07-14.xlsx
@@ -190,12 +190,12 @@
     <t>Deportivo Riestra</t>
   </si>
   <si>
+    <t>Athletic Club</t>
+  </si>
+  <si>
     <t>Banfield</t>
   </si>
   <si>
-    <t>Athletic Club</t>
-  </si>
-  <si>
     <t>Retrô</t>
   </si>
   <si>
@@ -205,12 +205,12 @@
     <t>Juventude</t>
   </si>
   <si>
+    <t>Vélez Sarsfield</t>
+  </si>
+  <si>
     <t>Unión Santa Fe</t>
   </si>
   <si>
-    <t>Vélez Sarsfield</t>
-  </si>
-  <si>
     <t>Botafogo SP</t>
   </si>
   <si>
@@ -226,12 +226,12 @@
     <t>Lanús</t>
   </si>
   <si>
+    <t>Avaí</t>
+  </si>
+  <si>
     <t>Defensa y Justicia</t>
   </si>
   <si>
-    <t>Avaí</t>
-  </si>
-  <si>
     <t>CSA</t>
   </si>
   <si>
@@ -241,10 +241,10 @@
     <t>Sport Recife</t>
   </si>
   <si>
+    <t>Tigre</t>
+  </si>
+  <si>
     <t>Estudiantes</t>
-  </si>
-  <si>
-    <t>Tigre</t>
   </si>
   <si>
     <t>Volta Redonda</t>
@@ -1208,7 +1208,7 @@
         <v>42</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s">
         <v>53</v>
@@ -1235,76 +1235,76 @@
         <v>78</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ6" t="s">
         <v>79</v>
@@ -1330,10 +1330,10 @@
         <v>53</v>
       </c>
       <c r="E7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1351,76 +1351,76 @@
         <v>78</v>
       </c>
       <c r="L7">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M7">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N7">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O7">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P7">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Q7">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R7">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S7">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T7">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U7">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V7">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W7">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X7">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y7">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Z7">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA7">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AB7">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC7">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD7">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AE7">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AF7">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG7">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH7">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="AI7">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="s">
         <v>79</v>
@@ -1440,7 +1440,7 @@
         <v>42</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
         <v>53</v>
@@ -1467,73 +1467,73 @@
         <v>78</v>
       </c>
       <c r="L8">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="M8">
         <v>2.9</v>
       </c>
       <c r="N8">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="O8">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="P8">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="Q8">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R8">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="S8">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="T8">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U8">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="V8">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="W8">
         <v>1.05</v>
       </c>
       <c r="X8">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y8">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Z8">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AA8">
+        <v>2.38</v>
+      </c>
+      <c r="AB8">
         <v>2.5</v>
-      </c>
-      <c r="AB8">
-        <v>2.4</v>
       </c>
       <c r="AC8">
         <v>1.5</v>
       </c>
       <c r="AD8">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="AE8">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AF8">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG8">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AH8">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="AI8">
         <v>1.05</v>
@@ -1931,76 +1931,76 @@
         <v>78</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ12" t="s">
         <v>79</v>
@@ -2047,76 +2047,76 @@
         <v>78</v>
       </c>
       <c r="L13">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="M13">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="N13">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="O13">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="P13">
+        <v>6.5</v>
+      </c>
+      <c r="Q13">
+        <v>2.25</v>
+      </c>
+      <c r="R13">
+        <v>1.53</v>
+      </c>
+      <c r="S13">
+        <v>2.38</v>
+      </c>
+      <c r="T13">
+        <v>3.5</v>
+      </c>
+      <c r="U13">
+        <v>1.29</v>
+      </c>
+      <c r="V13">
+        <v>11</v>
+      </c>
+      <c r="W13">
+        <v>1.05</v>
+      </c>
+      <c r="X13">
+        <v>1.1</v>
+      </c>
+      <c r="Y13">
+        <v>6.5</v>
+      </c>
+      <c r="Z13">
+        <v>1.48</v>
+      </c>
+      <c r="AA13">
+        <v>2.43</v>
+      </c>
+      <c r="AB13">
+        <v>2.5</v>
+      </c>
+      <c r="AC13">
+        <v>1.5</v>
+      </c>
+      <c r="AD13">
         <v>5</v>
       </c>
-      <c r="Q13">
-        <v>2.88</v>
-      </c>
-      <c r="R13">
-        <v>1.67</v>
-      </c>
-      <c r="S13">
-        <v>2.1</v>
-      </c>
-      <c r="T13">
-        <v>4.33</v>
-      </c>
-      <c r="U13">
-        <v>1.2</v>
-      </c>
-      <c r="V13">
-        <v>15</v>
-      </c>
-      <c r="W13">
-        <v>1.03</v>
-      </c>
-      <c r="X13">
-        <v>1.14</v>
-      </c>
-      <c r="Y13">
-        <v>5.5</v>
-      </c>
-      <c r="Z13">
-        <v>1.58</v>
-      </c>
-      <c r="AA13">
-        <v>2.18</v>
-      </c>
-      <c r="AB13">
-        <v>3.1</v>
-      </c>
-      <c r="AC13">
-        <v>1.36</v>
-      </c>
-      <c r="AD13">
-        <v>6.5</v>
-      </c>
       <c r="AE13">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AF13">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AG13">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AH13">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="AI13">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AJ13" t="s">
         <v>79</v>
@@ -2142,10 +2142,10 @@
         <v>53</v>
       </c>
       <c r="E14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2258,10 +2258,10 @@
         <v>53</v>
       </c>
       <c r="E15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2279,76 +2279,76 @@
         <v>78</v>
       </c>
       <c r="L15">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="M15">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N15">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O15">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="P15">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Q15">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="R15">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="S15">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T15">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U15">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V15">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="W15">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X15">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y15">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="Z15">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA15">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AB15">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC15">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD15">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE15">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AF15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG15">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AH15">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="AI15">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="s">
         <v>79</v>

--- a/jogos_2025-07-14.xlsx
+++ b/jogos_2025-07-14.xlsx
@@ -190,12 +190,12 @@
     <t>Deportivo Riestra</t>
   </si>
   <si>
+    <t>Banfield</t>
+  </si>
+  <si>
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>Banfield</t>
-  </si>
-  <si>
     <t>Retrô</t>
   </si>
   <si>
@@ -205,12 +205,12 @@
     <t>Juventude</t>
   </si>
   <si>
+    <t>Unión Santa Fe</t>
+  </si>
+  <si>
     <t>Vélez Sarsfield</t>
   </si>
   <si>
-    <t>Unión Santa Fe</t>
-  </si>
-  <si>
     <t>Botafogo SP</t>
   </si>
   <si>
@@ -226,12 +226,12 @@
     <t>Lanús</t>
   </si>
   <si>
+    <t>Defensa y Justicia</t>
+  </si>
+  <si>
     <t>Avaí</t>
   </si>
   <si>
-    <t>Defensa y Justicia</t>
-  </si>
-  <si>
     <t>CSA</t>
   </si>
   <si>
@@ -241,10 +241,10 @@
     <t>Sport Recife</t>
   </si>
   <si>
+    <t>Estudiantes</t>
+  </si>
+  <si>
     <t>Tigre</t>
-  </si>
-  <si>
-    <t>Estudiantes</t>
   </si>
   <si>
     <t>Volta Redonda</t>
@@ -887,13 +887,13 @@
         <v>78</v>
       </c>
       <c r="L3">
-        <v>2.75</v>
+        <v>2.98</v>
       </c>
       <c r="M3">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N3">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="O3">
         <v>1.98</v>
@@ -908,19 +908,19 @@
         <v>1.25</v>
       </c>
       <c r="S3">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="T3">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="U3">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="V3">
-        <v>4.6</v>
+        <v>4.95</v>
       </c>
       <c r="W3">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="X3">
         <v>1.03</v>
@@ -935,13 +935,13 @@
         <v>4.75</v>
       </c>
       <c r="AB3">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AC3">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AD3">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AE3">
         <v>1.53</v>
@@ -950,10 +950,10 @@
         <v>1.51</v>
       </c>
       <c r="AG3">
-        <v>2.41</v>
+        <v>2.51</v>
       </c>
       <c r="AH3">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AI3">
         <v>1.2</v>
@@ -1003,13 +1003,13 @@
         <v>78</v>
       </c>
       <c r="L4">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="M4">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="N4">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="O4">
         <v>2.21</v>
@@ -1021,55 +1021,55 @@
         <v>1.59</v>
       </c>
       <c r="R4">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="S4">
         <v>5</v>
       </c>
       <c r="T4">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U4">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="V4">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="W4">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y4">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="Z4">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AA4">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="AB4">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="AC4">
-        <v>3.9</v>
+        <v>3.73</v>
       </c>
       <c r="AD4">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AE4">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AF4">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AG4">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AH4">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AI4">
         <v>1.59</v>
@@ -1208,7 +1208,7 @@
         <v>42</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D6" t="s">
         <v>53</v>
@@ -1235,55 +1235,55 @@
         <v>78</v>
       </c>
       <c r="L6">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="M6">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N6">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="O6">
         <v>1.83</v>
       </c>
       <c r="P6">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="Q6">
         <v>2.4</v>
       </c>
       <c r="R6">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="S6">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="T6">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U6">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="V6">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="W6">
         <v>1.05</v>
       </c>
       <c r="X6">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y6">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Z6">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AA6">
+        <v>2.38</v>
+      </c>
+      <c r="AB6">
         <v>2.5</v>
-      </c>
-      <c r="AB6">
-        <v>2.4</v>
       </c>
       <c r="AC6">
         <v>1.5</v>
@@ -1292,16 +1292,16 @@
         <v>5</v>
       </c>
       <c r="AE6">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AF6">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG6">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AH6">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="AI6">
         <v>1.05</v>
@@ -1330,10 +1330,10 @@
         <v>53</v>
       </c>
       <c r="E7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1351,76 +1351,76 @@
         <v>78</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AJ7" t="s">
         <v>79</v>
@@ -1440,7 +1440,7 @@
         <v>42</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D8" t="s">
         <v>53</v>
@@ -1467,52 +1467,52 @@
         <v>78</v>
       </c>
       <c r="L8">
-        <v>2.35</v>
+        <v>2.46</v>
       </c>
       <c r="M8">
+        <v>2.71</v>
+      </c>
+      <c r="N8">
         <v>2.9</v>
       </c>
-      <c r="N8">
-        <v>3.4</v>
-      </c>
       <c r="O8">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="P8">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q8">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R8">
         <v>1.53</v>
       </c>
       <c r="S8">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="T8">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="U8">
         <v>1.29</v>
       </c>
       <c r="V8">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="W8">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X8">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Y8">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="Z8">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AA8">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AB8">
         <v>2.5</v>
@@ -1521,19 +1521,19 @@
         <v>1.5</v>
       </c>
       <c r="AD8">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AE8">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF8">
         <v>2.05</v>
       </c>
       <c r="AG8">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AH8">
-        <v>9.5</v>
+        <v>9.75</v>
       </c>
       <c r="AI8">
         <v>1.05</v>
@@ -1601,13 +1601,13 @@
         <v>2.4</v>
       </c>
       <c r="R9">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="S9">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="T9">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="U9">
         <v>1.22</v>
@@ -1625,19 +1625,19 @@
         <v>5.5</v>
       </c>
       <c r="Z9">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AA9">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="AB9">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="AC9">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AD9">
-        <v>5.35</v>
+        <v>5.45</v>
       </c>
       <c r="AE9">
         <v>1.09</v>
@@ -1702,10 +1702,10 @@
         <v>1.68</v>
       </c>
       <c r="M10">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="N10">
-        <v>4.88</v>
+        <v>5.1</v>
       </c>
       <c r="O10">
         <v>1.53</v>
@@ -1717,10 +1717,10 @@
         <v>3.1</v>
       </c>
       <c r="R10">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="S10">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="T10">
         <v>3.6</v>
@@ -1729,46 +1729,46 @@
         <v>1.3</v>
       </c>
       <c r="V10">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="W10">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X10">
         <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Z10">
         <v>1.39</v>
       </c>
       <c r="AA10">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="AB10">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="AC10">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AD10">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AE10">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF10">
         <v>2.25</v>
       </c>
       <c r="AG10">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AH10">
-        <v>9.300000000000001</v>
+        <v>10</v>
       </c>
       <c r="AI10">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AJ10" t="s">
         <v>79</v>
@@ -1815,13 +1815,13 @@
         <v>78</v>
       </c>
       <c r="L11">
-        <v>2.24</v>
+        <v>2.45</v>
       </c>
       <c r="M11">
         <v>2.85</v>
       </c>
       <c r="N11">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="O11">
         <v>1.83</v>
@@ -1833,34 +1833,34 @@
         <v>2.25</v>
       </c>
       <c r="R11">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="S11">
-        <v>2.66</v>
+        <v>2.61</v>
       </c>
       <c r="T11">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="U11">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="V11">
-        <v>8.300000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="W11">
         <v>1.06</v>
       </c>
       <c r="X11">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y11">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="Z11">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AA11">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="AB11">
         <v>2.25</v>
@@ -1869,10 +1869,10 @@
         <v>1.63</v>
       </c>
       <c r="AD11">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AE11">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF11">
         <v>1.85</v>
@@ -1881,7 +1881,7 @@
         <v>1.85</v>
       </c>
       <c r="AH11">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="AI11">
         <v>1.06</v>
@@ -1931,76 +1931,76 @@
         <v>78</v>
       </c>
       <c r="L12">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="M12">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="N12">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="O12">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="P12">
+        <v>6</v>
+      </c>
+      <c r="Q12">
+        <v>2.25</v>
+      </c>
+      <c r="R12">
+        <v>1.53</v>
+      </c>
+      <c r="S12">
+        <v>2.38</v>
+      </c>
+      <c r="T12">
+        <v>3.75</v>
+      </c>
+      <c r="U12">
+        <v>1.25</v>
+      </c>
+      <c r="V12">
+        <v>11</v>
+      </c>
+      <c r="W12">
+        <v>1.05</v>
+      </c>
+      <c r="X12">
+        <v>1.11</v>
+      </c>
+      <c r="Y12">
+        <v>6.25</v>
+      </c>
+      <c r="Z12">
+        <v>1.48</v>
+      </c>
+      <c r="AA12">
+        <v>2.43</v>
+      </c>
+      <c r="AB12">
+        <v>2.6</v>
+      </c>
+      <c r="AC12">
+        <v>1.48</v>
+      </c>
+      <c r="AD12">
         <v>5</v>
       </c>
-      <c r="Q12">
-        <v>2.88</v>
-      </c>
-      <c r="R12">
-        <v>1.67</v>
-      </c>
-      <c r="S12">
-        <v>2.1</v>
-      </c>
-      <c r="T12">
-        <v>4.33</v>
-      </c>
-      <c r="U12">
-        <v>1.2</v>
-      </c>
-      <c r="V12">
-        <v>15</v>
-      </c>
-      <c r="W12">
-        <v>1.03</v>
-      </c>
-      <c r="X12">
-        <v>1.14</v>
-      </c>
-      <c r="Y12">
-        <v>5.5</v>
-      </c>
-      <c r="Z12">
-        <v>1.58</v>
-      </c>
-      <c r="AA12">
-        <v>2.18</v>
-      </c>
-      <c r="AB12">
-        <v>3.1</v>
-      </c>
-      <c r="AC12">
-        <v>1.36</v>
-      </c>
-      <c r="AD12">
-        <v>6.5</v>
-      </c>
       <c r="AE12">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AF12">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="AG12">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AH12">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI12">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AJ12" t="s">
         <v>79</v>
@@ -2026,10 +2026,10 @@
         <v>53</v>
       </c>
       <c r="E13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2142,10 +2142,10 @@
         <v>53</v>
       </c>
       <c r="E14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2163,76 +2163,76 @@
         <v>78</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH14">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AI14">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ14" t="s">
         <v>79</v>
@@ -2279,76 +2279,76 @@
         <v>78</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH15">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AI15">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AJ15" t="s">
         <v>79</v>
@@ -2395,13 +2395,13 @@
         <v>78</v>
       </c>
       <c r="L16">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="M16">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="N16">
-        <v>3.38</v>
+        <v>3.06</v>
       </c>
       <c r="O16">
         <v>1.83</v>
@@ -2413,46 +2413,46 @@
         <v>2.5</v>
       </c>
       <c r="R16">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="S16">
         <v>2.2</v>
       </c>
       <c r="T16">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="U16">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="V16">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="W16">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X16">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Y16">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="Z16">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AA16">
         <v>2.2</v>
       </c>
       <c r="AB16">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="AC16">
         <v>1.38</v>
       </c>
       <c r="AD16">
-        <v>5.8</v>
+        <v>5.65</v>
       </c>
       <c r="AE16">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AF16">
         <v>2.3</v>
@@ -2461,7 +2461,7 @@
         <v>1.57</v>
       </c>
       <c r="AH16">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AI16">
         <v>1.01</v>

--- a/jogos_2025-07-14.xlsx
+++ b/jogos_2025-07-14.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="89">
   <si>
     <t>Date</t>
   </si>
@@ -130,6 +130,9 @@
     <t>DateTime</t>
   </si>
   <si>
+    <t>12:00</t>
+  </si>
+  <si>
     <t>14:00</t>
   </si>
   <si>
@@ -157,6 +160,9 @@
     <t>21:30</t>
   </si>
   <si>
+    <t>Finland Veikkausliiga</t>
+  </si>
+  <si>
     <t>Sweden Allsvenskan</t>
   </si>
   <si>
@@ -178,6 +184,9 @@
     <t>2025</t>
   </si>
   <si>
+    <t>Ilves</t>
+  </si>
+  <si>
     <t>Sirius</t>
   </si>
   <si>
@@ -190,12 +199,12 @@
     <t>Deportivo Riestra</t>
   </si>
   <si>
+    <t>Athletic Club</t>
+  </si>
+  <si>
     <t>Banfield</t>
   </si>
   <si>
-    <t>Athletic Club</t>
-  </si>
-  <si>
     <t>Retrô</t>
   </si>
   <si>
@@ -205,15 +214,18 @@
     <t>Juventude</t>
   </si>
   <si>
+    <t>Vélez Sarsfield</t>
+  </si>
+  <si>
     <t>Unión Santa Fe</t>
   </si>
   <si>
-    <t>Vélez Sarsfield</t>
-  </si>
-  <si>
     <t>Botafogo SP</t>
   </si>
   <si>
+    <t>VPS</t>
+  </si>
+  <si>
     <t>Mjällby</t>
   </si>
   <si>
@@ -226,12 +238,12 @@
     <t>Lanús</t>
   </si>
   <si>
+    <t>Avaí</t>
+  </si>
+  <si>
     <t>Defensa y Justicia</t>
   </si>
   <si>
-    <t>Avaí</t>
-  </si>
-  <si>
     <t>CSA</t>
   </si>
   <si>
@@ -241,19 +253,34 @@
     <t>Sport Recife</t>
   </si>
   <si>
+    <t>Tigre</t>
+  </si>
+  <si>
     <t>Estudiantes</t>
   </si>
   <si>
-    <t>Tigre</t>
-  </si>
-  <si>
     <t>Volta Redonda</t>
   </si>
   <si>
+    <t>complete</t>
+  </si>
+  <si>
     <t>incomplete</t>
   </si>
   <si>
+    <t>['22', '84', '89']</t>
+  </si>
+  <si>
+    <t>['80']</t>
+  </si>
+  <si>
     <t>[]</t>
+  </si>
+  <si>
+    <t>['47', '74']</t>
+  </si>
+  <si>
+    <t>['7', '16']</t>
   </si>
 </sst>
 </file>
@@ -617,7 +644,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL16"/>
+  <dimension ref="A1:AL17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:38">
@@ -744,112 +771,112 @@
         <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="L2">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="M2">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="S2">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="T2">
-        <v>2.38</v>
+        <v>2.19</v>
       </c>
       <c r="U2">
-        <v>1.53</v>
+        <v>1.74</v>
       </c>
       <c r="V2">
-        <v>6</v>
+        <v>4.8</v>
       </c>
       <c r="W2">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="X2">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="Z2">
+        <v>1.15</v>
+      </c>
+      <c r="AA2">
+        <v>5</v>
+      </c>
+      <c r="AB2">
+        <v>1.47</v>
+      </c>
+      <c r="AC2">
+        <v>2.75</v>
+      </c>
+      <c r="AD2">
+        <v>2.19</v>
+      </c>
+      <c r="AE2">
+        <v>1.74</v>
+      </c>
+      <c r="AF2">
+        <v>1.65</v>
+      </c>
+      <c r="AG2">
+        <v>2.15</v>
+      </c>
+      <c r="AH2">
+        <v>4</v>
+      </c>
+      <c r="AI2">
         <v>1.22</v>
       </c>
-      <c r="AA2">
-        <v>4.33</v>
-      </c>
-      <c r="AB2">
-        <v>1.56</v>
-      </c>
-      <c r="AC2">
-        <v>2.27</v>
-      </c>
-      <c r="AD2">
-        <v>2.65</v>
-      </c>
-      <c r="AE2">
-        <v>1.48</v>
-      </c>
-      <c r="AF2">
-        <v>1.57</v>
-      </c>
-      <c r="AG2">
-        <v>2.25</v>
-      </c>
-      <c r="AH2">
-        <v>4.75</v>
-      </c>
-      <c r="AI2">
-        <v>1.2</v>
-      </c>
       <c r="AJ2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="AK2" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AL2" s="3">
-        <v>45852.58333333334</v>
+        <v>45852.5</v>
       </c>
     </row>
     <row r="3" spans="1:38">
@@ -860,112 +887,112 @@
         <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K3" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="L3">
-        <v>2.98</v>
+        <v>3.3</v>
       </c>
       <c r="M3">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N3">
-        <v>2.11</v>
+        <v>1.89</v>
       </c>
       <c r="O3">
-        <v>1.98</v>
+        <v>2.4</v>
       </c>
       <c r="P3">
-        <v>14.75</v>
+        <v>11.5</v>
       </c>
       <c r="Q3">
-        <v>1.88</v>
+        <v>1.57</v>
       </c>
       <c r="R3">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S3">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="T3">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="U3">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="V3">
-        <v>4.95</v>
+        <v>6</v>
       </c>
       <c r="W3">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="X3">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y3">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Z3">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AA3">
+        <v>4.33</v>
+      </c>
+      <c r="AB3">
+        <v>1.56</v>
+      </c>
+      <c r="AC3">
+        <v>2.27</v>
+      </c>
+      <c r="AD3">
+        <v>2.65</v>
+      </c>
+      <c r="AE3">
+        <v>1.48</v>
+      </c>
+      <c r="AF3">
+        <v>1.57</v>
+      </c>
+      <c r="AG3">
+        <v>2.25</v>
+      </c>
+      <c r="AH3">
         <v>4.75</v>
-      </c>
-      <c r="AB3">
-        <v>1.53</v>
-      </c>
-      <c r="AC3">
-        <v>2.25</v>
-      </c>
-      <c r="AD3">
-        <v>2.4</v>
-      </c>
-      <c r="AE3">
-        <v>1.53</v>
-      </c>
-      <c r="AF3">
-        <v>1.51</v>
-      </c>
-      <c r="AG3">
-        <v>2.51</v>
-      </c>
-      <c r="AH3">
-        <v>3.9</v>
       </c>
       <c r="AI3">
         <v>1.2</v>
       </c>
       <c r="AJ3" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="AK3" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AL3" s="3">
-        <v>45852.64583333334</v>
+        <v>45852.58333333334</v>
       </c>
     </row>
     <row r="4" spans="1:38">
@@ -976,16 +1003,16 @@
         <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -1000,88 +1027,88 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="L4">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="M4">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="N4">
-        <v>1.71</v>
+        <v>2.44</v>
       </c>
       <c r="O4">
-        <v>2.21</v>
+        <v>1.98</v>
       </c>
       <c r="P4">
-        <v>43</v>
+        <v>14.75</v>
       </c>
       <c r="Q4">
-        <v>1.59</v>
+        <v>1.88</v>
       </c>
       <c r="R4">
+        <v>1.25</v>
+      </c>
+      <c r="S4">
+        <v>3.7</v>
+      </c>
+      <c r="T4">
+        <v>2.25</v>
+      </c>
+      <c r="U4">
+        <v>1.6</v>
+      </c>
+      <c r="V4">
+        <v>4.6</v>
+      </c>
+      <c r="W4">
+        <v>1.15</v>
+      </c>
+      <c r="X4">
+        <v>1.03</v>
+      </c>
+      <c r="Y4">
+        <v>12</v>
+      </c>
+      <c r="Z4">
         <v>1.13</v>
       </c>
-      <c r="S4">
+      <c r="AA4">
         <v>5</v>
       </c>
-      <c r="T4">
-        <v>1.74</v>
-      </c>
-      <c r="U4">
-        <v>2.15</v>
-      </c>
-      <c r="V4">
-        <v>2.9</v>
-      </c>
-      <c r="W4">
-        <v>1.31</v>
-      </c>
-      <c r="X4">
-        <v>1.01</v>
-      </c>
-      <c r="Y4">
-        <v>28</v>
-      </c>
-      <c r="Z4">
-        <v>1.05</v>
-      </c>
-      <c r="AA4">
-        <v>11</v>
-      </c>
       <c r="AB4">
-        <v>1.23</v>
+        <v>1.5</v>
       </c>
       <c r="AC4">
-        <v>3.73</v>
+        <v>2.45</v>
       </c>
       <c r="AD4">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="AE4">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="AF4">
+        <v>1.42</v>
+      </c>
+      <c r="AG4">
+        <v>2.5</v>
+      </c>
+      <c r="AH4">
+        <v>3.6</v>
+      </c>
+      <c r="AI4">
         <v>1.25</v>
       </c>
-      <c r="AG4">
-        <v>3.7</v>
-      </c>
-      <c r="AH4">
-        <v>2.3</v>
-      </c>
-      <c r="AI4">
-        <v>1.59</v>
-      </c>
       <c r="AJ4" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AK4" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AL4" s="3">
-        <v>45852.67708333334</v>
+        <v>45852.64583333334</v>
       </c>
     </row>
     <row r="5" spans="1:38">
@@ -1092,16 +1119,16 @@
         <v>41</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F5" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1116,88 +1143,88 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="L5">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="M5">
-        <v>2.75</v>
+        <v>4.62</v>
       </c>
       <c r="N5">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="O5">
-        <v>2.5</v>
+        <v>2.21</v>
       </c>
       <c r="P5">
+        <v>43</v>
+      </c>
+      <c r="Q5">
+        <v>1.59</v>
+      </c>
+      <c r="R5">
+        <v>1.14</v>
+      </c>
+      <c r="S5">
         <v>5</v>
       </c>
-      <c r="Q5">
-        <v>1.91</v>
-      </c>
-      <c r="R5">
-        <v>1.67</v>
-      </c>
-      <c r="S5">
-        <v>2.1</v>
-      </c>
       <c r="T5">
-        <v>4.33</v>
+        <v>1.65</v>
       </c>
       <c r="U5">
+        <v>2.11</v>
+      </c>
+      <c r="V5">
+        <v>3.1</v>
+      </c>
+      <c r="W5">
+        <v>1.33</v>
+      </c>
+      <c r="X5">
+        <v>1</v>
+      </c>
+      <c r="Y5">
+        <v>29</v>
+      </c>
+      <c r="Z5">
+        <v>1.02</v>
+      </c>
+      <c r="AA5">
+        <v>9.5</v>
+      </c>
+      <c r="AB5">
         <v>1.2</v>
       </c>
-      <c r="V5">
-        <v>15</v>
-      </c>
-      <c r="W5">
-        <v>1.03</v>
-      </c>
-      <c r="X5">
-        <v>1.15</v>
-      </c>
-      <c r="Y5">
-        <v>5.25</v>
-      </c>
-      <c r="Z5">
-        <v>1.63</v>
-      </c>
-      <c r="AA5">
-        <v>2.1</v>
-      </c>
-      <c r="AB5">
-        <v>3.1</v>
-      </c>
       <c r="AC5">
-        <v>1.36</v>
+        <v>3.9</v>
       </c>
       <c r="AD5">
-        <v>6.5</v>
+        <v>1.57</v>
       </c>
       <c r="AE5">
-        <v>1.1</v>
+        <v>2.38</v>
       </c>
       <c r="AF5">
-        <v>2.38</v>
+        <v>1.25</v>
       </c>
       <c r="AG5">
-        <v>1.53</v>
+        <v>3.75</v>
       </c>
       <c r="AH5">
-        <v>11</v>
+        <v>2.15</v>
       </c>
       <c r="AI5">
-        <v>1.03</v>
+        <v>1.6</v>
       </c>
       <c r="AJ5" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AK5" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AL5" s="3">
-        <v>45852.6875</v>
+        <v>45852.67708333334</v>
       </c>
     </row>
     <row r="6" spans="1:38">
@@ -1208,16 +1235,16 @@
         <v>42</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F6" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -1232,88 +1259,88 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="L6">
-        <v>2.45</v>
+        <v>3.25</v>
       </c>
       <c r="M6">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="N6">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="O6">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="P6">
+        <v>5</v>
+      </c>
+      <c r="Q6">
+        <v>1.91</v>
+      </c>
+      <c r="R6">
+        <v>1.67</v>
+      </c>
+      <c r="S6">
+        <v>2.1</v>
+      </c>
+      <c r="T6">
+        <v>4.33</v>
+      </c>
+      <c r="U6">
+        <v>1.2</v>
+      </c>
+      <c r="V6">
+        <v>15</v>
+      </c>
+      <c r="W6">
+        <v>1.03</v>
+      </c>
+      <c r="X6">
+        <v>1.15</v>
+      </c>
+      <c r="Y6">
+        <v>5.25</v>
+      </c>
+      <c r="Z6">
+        <v>1.63</v>
+      </c>
+      <c r="AA6">
+        <v>2.1</v>
+      </c>
+      <c r="AB6">
+        <v>3.1</v>
+      </c>
+      <c r="AC6">
+        <v>1.36</v>
+      </c>
+      <c r="AD6">
         <v>6.5</v>
       </c>
-      <c r="Q6">
-        <v>2.4</v>
-      </c>
-      <c r="R6">
+      <c r="AE6">
+        <v>1.1</v>
+      </c>
+      <c r="AF6">
+        <v>2.38</v>
+      </c>
+      <c r="AG6">
         <v>1.53</v>
       </c>
-      <c r="S6">
-        <v>2.38</v>
-      </c>
-      <c r="T6">
-        <v>3.5</v>
-      </c>
-      <c r="U6">
-        <v>1.29</v>
-      </c>
-      <c r="V6">
+      <c r="AH6">
         <v>11</v>
       </c>
-      <c r="W6">
-        <v>1.05</v>
-      </c>
-      <c r="X6">
-        <v>1.1</v>
-      </c>
-      <c r="Y6">
-        <v>6.5</v>
-      </c>
-      <c r="Z6">
-        <v>1.5</v>
-      </c>
-      <c r="AA6">
-        <v>2.38</v>
-      </c>
-      <c r="AB6">
-        <v>2.5</v>
-      </c>
-      <c r="AC6">
-        <v>1.5</v>
-      </c>
-      <c r="AD6">
-        <v>5</v>
-      </c>
-      <c r="AE6">
-        <v>1.17</v>
-      </c>
-      <c r="AF6">
-        <v>2.05</v>
-      </c>
-      <c r="AG6">
-        <v>1.7</v>
-      </c>
-      <c r="AH6">
-        <v>9.5</v>
-      </c>
       <c r="AI6">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AJ6" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AK6" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AL6" s="3">
-        <v>45852.79166666666</v>
+        <v>45852.6875</v>
       </c>
     </row>
     <row r="7" spans="1:38">
@@ -1321,19 +1348,19 @@
         <v>45852</v>
       </c>
       <c r="B7" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F7" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -1348,40 +1375,40 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="L7">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="M7">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="N7">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="O7">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="P7">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q7">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R7">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="S7">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="T7">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U7">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="V7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W7">
         <v>1.05</v>
@@ -1390,43 +1417,43 @@
         <v>1.1</v>
       </c>
       <c r="Y7">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="Z7">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AA7">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AB7">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AC7">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AD7">
-        <v>4.75</v>
+        <v>4.5</v>
       </c>
       <c r="AE7">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF7">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG7">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AH7">
         <v>9.5</v>
       </c>
       <c r="AI7">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AJ7" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AK7" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AL7" s="3">
         <v>45852.79166666666</v>
@@ -1437,19 +1464,19 @@
         <v>45852</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E8" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F8" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1464,55 +1491,55 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="L8">
-        <v>2.46</v>
+        <v>2.35</v>
       </c>
       <c r="M8">
-        <v>2.71</v>
+        <v>2.9</v>
       </c>
       <c r="N8">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="O8">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="P8">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="Q8">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R8">
         <v>1.53</v>
       </c>
       <c r="S8">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="T8">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U8">
         <v>1.29</v>
       </c>
       <c r="V8">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="W8">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X8">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Y8">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Z8">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AA8">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AB8">
         <v>2.5</v>
@@ -1521,28 +1548,28 @@
         <v>1.5</v>
       </c>
       <c r="AD8">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="AE8">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF8">
         <v>2.05</v>
       </c>
       <c r="AG8">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AH8">
-        <v>9.75</v>
+        <v>9.5</v>
       </c>
       <c r="AI8">
         <v>1.05</v>
       </c>
       <c r="AJ8" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AK8" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AL8" s="3">
         <v>45852.79166666666</v>
@@ -1559,13 +1586,13 @@
         <v>51</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F9" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1580,88 +1607,88 @@
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="L9">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="M9">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="N9">
-        <v>3.03</v>
+        <v>3.3</v>
       </c>
       <c r="O9">
         <v>1.83</v>
       </c>
       <c r="P9">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="Q9">
         <v>2.4</v>
       </c>
       <c r="R9">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="S9">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="T9">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U9">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="V9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="W9">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X9">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Y9">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="Z9">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AA9">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="AB9">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="AC9">
-        <v>1.41</v>
+        <v>1.5</v>
       </c>
       <c r="AD9">
-        <v>5.45</v>
+        <v>5</v>
       </c>
       <c r="AE9">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="AF9">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="AG9">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AH9">
-        <v>11.5</v>
+        <v>9.5</v>
       </c>
       <c r="AI9">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AJ9" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AK9" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AL9" s="3">
-        <v>45852.8125</v>
+        <v>45852.79166666666</v>
       </c>
     </row>
     <row r="10" spans="1:38">
@@ -1669,19 +1696,19 @@
         <v>45852</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D10" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E10" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F10" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1696,85 +1723,85 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="L10">
-        <v>1.68</v>
+        <v>2.65</v>
       </c>
       <c r="M10">
-        <v>3.26</v>
+        <v>2.65</v>
       </c>
       <c r="N10">
-        <v>5.1</v>
+        <v>2.7</v>
       </c>
       <c r="O10">
+        <v>1.83</v>
+      </c>
+      <c r="P10">
+        <v>5.5</v>
+      </c>
+      <c r="Q10">
+        <v>2.4</v>
+      </c>
+      <c r="R10">
         <v>1.53</v>
       </c>
-      <c r="P10">
-        <v>8.1</v>
-      </c>
-      <c r="Q10">
-        <v>3.1</v>
-      </c>
-      <c r="R10">
-        <v>1.47</v>
-      </c>
       <c r="S10">
-        <v>2.47</v>
+        <v>2.38</v>
       </c>
       <c r="T10">
         <v>3.6</v>
       </c>
       <c r="U10">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="V10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W10">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X10">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="Y10">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="Z10">
-        <v>1.39</v>
+        <v>1.5</v>
       </c>
       <c r="AA10">
-        <v>2.6</v>
+        <v>2.38</v>
       </c>
       <c r="AB10">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="AC10">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AD10">
-        <v>4.5</v>
+        <v>5.35</v>
       </c>
       <c r="AE10">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AF10">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AG10">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AH10">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AI10">
         <v>1.02</v>
       </c>
       <c r="AJ10" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AK10" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AL10" s="3">
         <v>45852.8125</v>
@@ -1788,16 +1815,16 @@
         <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F11" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1812,88 +1839,88 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="L11">
+        <v>1.72</v>
+      </c>
+      <c r="M11">
+        <v>3.25</v>
+      </c>
+      <c r="N11">
+        <v>4.5</v>
+      </c>
+      <c r="O11">
+        <v>1.53</v>
+      </c>
+      <c r="P11">
+        <v>8.1</v>
+      </c>
+      <c r="Q11">
+        <v>3.1</v>
+      </c>
+      <c r="R11">
+        <v>1.51</v>
+      </c>
+      <c r="S11">
         <v>2.45</v>
       </c>
-      <c r="M11">
-        <v>2.85</v>
-      </c>
-      <c r="N11">
-        <v>2.98</v>
-      </c>
-      <c r="O11">
-        <v>1.83</v>
-      </c>
-      <c r="P11">
-        <v>7.25</v>
-      </c>
-      <c r="Q11">
-        <v>2.25</v>
-      </c>
-      <c r="R11">
-        <v>1.52</v>
-      </c>
-      <c r="S11">
-        <v>2.61</v>
-      </c>
       <c r="T11">
-        <v>3.12</v>
+        <v>3.6</v>
       </c>
       <c r="U11">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="V11">
-        <v>7.8</v>
+        <v>9.25</v>
       </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X11">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="Z11">
         <v>1.4</v>
       </c>
       <c r="AA11">
-        <v>2.81</v>
+        <v>2.4</v>
       </c>
       <c r="AB11">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AC11">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="AD11">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AE11">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AF11">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="AG11">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AH11">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="AI11">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AJ11" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AK11" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AL11" s="3">
-        <v>45852.83333333334</v>
+        <v>45852.8125</v>
       </c>
     </row>
     <row r="12" spans="1:38">
@@ -1904,16 +1931,16 @@
         <v>45</v>
       </c>
       <c r="C12" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D12" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E12" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F12" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1928,88 +1955,88 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="L12">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="M12">
-        <v>2.9</v>
+        <v>3.13</v>
       </c>
       <c r="N12">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="O12">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="P12">
-        <v>6</v>
+        <v>7.25</v>
       </c>
       <c r="Q12">
         <v>2.25</v>
       </c>
       <c r="R12">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="S12">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T12">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="U12">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="V12">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="W12">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X12">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Y12">
-        <v>6.25</v>
+        <v>7.1</v>
       </c>
       <c r="Z12">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AA12">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="AB12">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="AC12">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AD12">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="AE12">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF12">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG12">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AH12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI12">
         <v>1.04</v>
       </c>
       <c r="AJ12" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AK12" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AL12" s="3">
-        <v>45852.88541666666</v>
+        <v>45852.83333333334</v>
       </c>
     </row>
     <row r="13" spans="1:38">
@@ -2017,19 +2044,19 @@
         <v>45852</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E13" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F13" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -2044,85 +2071,85 @@
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="L13">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="M13">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="N13">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="O13">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="P13">
+        <v>5</v>
+      </c>
+      <c r="Q13">
+        <v>2.88</v>
+      </c>
+      <c r="R13">
+        <v>1.67</v>
+      </c>
+      <c r="S13">
+        <v>2.1</v>
+      </c>
+      <c r="T13">
+        <v>4.33</v>
+      </c>
+      <c r="U13">
+        <v>1.2</v>
+      </c>
+      <c r="V13">
+        <v>15</v>
+      </c>
+      <c r="W13">
+        <v>1.03</v>
+      </c>
+      <c r="X13">
+        <v>1.14</v>
+      </c>
+      <c r="Y13">
+        <v>5.5</v>
+      </c>
+      <c r="Z13">
+        <v>1.58</v>
+      </c>
+      <c r="AA13">
+        <v>2.18</v>
+      </c>
+      <c r="AB13">
+        <v>3.1</v>
+      </c>
+      <c r="AC13">
+        <v>1.36</v>
+      </c>
+      <c r="AD13">
         <v>6.5</v>
       </c>
-      <c r="Q13">
-        <v>2.25</v>
-      </c>
-      <c r="R13">
-        <v>1.53</v>
-      </c>
-      <c r="S13">
-        <v>2.38</v>
-      </c>
-      <c r="T13">
-        <v>3.5</v>
-      </c>
-      <c r="U13">
-        <v>1.29</v>
-      </c>
-      <c r="V13">
+      <c r="AE13">
+        <v>1.1</v>
+      </c>
+      <c r="AF13">
+        <v>2.5</v>
+      </c>
+      <c r="AG13">
+        <v>1.5</v>
+      </c>
+      <c r="AH13">
         <v>11</v>
       </c>
-      <c r="W13">
-        <v>1.05</v>
-      </c>
-      <c r="X13">
-        <v>1.1</v>
-      </c>
-      <c r="Y13">
-        <v>6.5</v>
-      </c>
-      <c r="Z13">
-        <v>1.48</v>
-      </c>
-      <c r="AA13">
-        <v>2.43</v>
-      </c>
-      <c r="AB13">
-        <v>2.5</v>
-      </c>
-      <c r="AC13">
-        <v>1.5</v>
-      </c>
-      <c r="AD13">
-        <v>5</v>
-      </c>
-      <c r="AE13">
-        <v>1.17</v>
-      </c>
-      <c r="AF13">
-        <v>2</v>
-      </c>
-      <c r="AG13">
-        <v>1.75</v>
-      </c>
-      <c r="AH13">
-        <v>9.5</v>
-      </c>
       <c r="AI13">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AJ13" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AK13" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AL13" s="3">
         <v>45852.88541666666</v>
@@ -2133,19 +2160,19 @@
         <v>45852</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D14" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E14" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F14" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -2160,73 +2187,73 @@
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="L14">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="M14">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="N14">
         <v>4.1</v>
       </c>
       <c r="O14">
+        <v>1.8</v>
+      </c>
+      <c r="P14">
+        <v>4.5</v>
+      </c>
+      <c r="Q14">
+        <v>3</v>
+      </c>
+      <c r="R14">
         <v>1.73</v>
       </c>
-      <c r="P14">
+      <c r="S14">
+        <v>2</v>
+      </c>
+      <c r="T14">
         <v>5</v>
       </c>
-      <c r="Q14">
-        <v>2.88</v>
-      </c>
-      <c r="R14">
-        <v>1.67</v>
-      </c>
-      <c r="S14">
-        <v>2.1</v>
-      </c>
-      <c r="T14">
-        <v>4.33</v>
-      </c>
       <c r="U14">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="V14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="W14">
         <v>1.03</v>
       </c>
       <c r="X14">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="Y14">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="Z14">
-        <v>1.58</v>
+        <v>1.81</v>
       </c>
       <c r="AA14">
-        <v>2.18</v>
+        <v>2.07</v>
       </c>
       <c r="AB14">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="AC14">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AD14">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AE14">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AF14">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AG14">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AH14">
         <v>11</v>
@@ -2235,10 +2262,10 @@
         <v>1.03</v>
       </c>
       <c r="AJ14" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AK14" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AL14" s="3">
         <v>45852.88541666666</v>
@@ -2249,19 +2276,19 @@
         <v>45852</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C15" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D15" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E15" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F15" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -2276,85 +2303,85 @@
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="L15">
-        <v>2.3</v>
+        <v>2.63</v>
       </c>
       <c r="M15">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="N15">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="O15">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="P15">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="Q15">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="R15">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="S15">
+        <v>2.38</v>
+      </c>
+      <c r="T15">
+        <v>3.5</v>
+      </c>
+      <c r="U15">
+        <v>1.29</v>
+      </c>
+      <c r="V15">
+        <v>11</v>
+      </c>
+      <c r="W15">
+        <v>1.05</v>
+      </c>
+      <c r="X15">
+        <v>1.1</v>
+      </c>
+      <c r="Y15">
+        <v>6.5</v>
+      </c>
+      <c r="Z15">
+        <v>1.48</v>
+      </c>
+      <c r="AA15">
+        <v>2.43</v>
+      </c>
+      <c r="AB15">
+        <v>2.5</v>
+      </c>
+      <c r="AC15">
+        <v>1.5</v>
+      </c>
+      <c r="AD15">
+        <v>5</v>
+      </c>
+      <c r="AE15">
+        <v>1.17</v>
+      </c>
+      <c r="AF15">
         <v>2</v>
       </c>
-      <c r="T15">
-        <v>5</v>
-      </c>
-      <c r="U15">
-        <v>1.17</v>
-      </c>
-      <c r="V15">
-        <v>17</v>
-      </c>
-      <c r="W15">
-        <v>1.03</v>
-      </c>
-      <c r="X15">
-        <v>1.17</v>
-      </c>
-      <c r="Y15">
-        <v>5</v>
-      </c>
-      <c r="Z15">
-        <v>1.81</v>
-      </c>
-      <c r="AA15">
-        <v>2.07</v>
-      </c>
-      <c r="AB15">
-        <v>3.5</v>
-      </c>
-      <c r="AC15">
-        <v>1.3</v>
-      </c>
-      <c r="AD15">
-        <v>7</v>
-      </c>
-      <c r="AE15">
-        <v>1.09</v>
-      </c>
-      <c r="AF15">
-        <v>2.63</v>
-      </c>
       <c r="AG15">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AH15">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="AI15">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AJ15" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AK15" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AL15" s="3">
         <v>45852.88541666666</v>
@@ -2368,16 +2395,16 @@
         <v>46</v>
       </c>
       <c r="C16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E16" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F16" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2392,87 +2419,203 @@
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="L16">
-        <v>2.27</v>
+        <v>2.75</v>
       </c>
       <c r="M16">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="N16">
-        <v>3.06</v>
+        <v>2.9</v>
       </c>
       <c r="O16">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="P16">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="Q16">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="R16">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="S16">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="T16">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="U16">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="V16">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="W16">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X16">
         <v>1.11</v>
       </c>
       <c r="Y16">
+        <v>6.25</v>
+      </c>
+      <c r="Z16">
+        <v>1.48</v>
+      </c>
+      <c r="AA16">
+        <v>2.43</v>
+      </c>
+      <c r="AB16">
+        <v>2.6</v>
+      </c>
+      <c r="AC16">
+        <v>1.48</v>
+      </c>
+      <c r="AD16">
+        <v>5</v>
+      </c>
+      <c r="AE16">
+        <v>1.17</v>
+      </c>
+      <c r="AF16">
+        <v>2.05</v>
+      </c>
+      <c r="AG16">
+        <v>1.7</v>
+      </c>
+      <c r="AH16">
+        <v>10</v>
+      </c>
+      <c r="AI16">
+        <v>1.04</v>
+      </c>
+      <c r="AJ16" t="s">
+        <v>86</v>
+      </c>
+      <c r="AK16" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL16" s="3">
+        <v>45852.88541666666</v>
+      </c>
+    </row>
+    <row r="17" spans="1:38">
+      <c r="A17" s="2">
+        <v>45852</v>
+      </c>
+      <c r="B17" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" t="s">
+        <v>55</v>
+      </c>
+      <c r="E17" t="s">
+        <v>68</v>
+      </c>
+      <c r="F17" t="s">
+        <v>81</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17" t="s">
+        <v>83</v>
+      </c>
+      <c r="L17">
+        <v>2.14</v>
+      </c>
+      <c r="M17">
+        <v>2.8</v>
+      </c>
+      <c r="N17">
+        <v>3.5</v>
+      </c>
+      <c r="O17">
+        <v>1.83</v>
+      </c>
+      <c r="P17">
         <v>5.5</v>
       </c>
-      <c r="Z16">
-        <v>1.55</v>
-      </c>
-      <c r="AA16">
-        <v>2.2</v>
-      </c>
-      <c r="AB16">
-        <v>2.81</v>
-      </c>
-      <c r="AC16">
-        <v>1.38</v>
-      </c>
-      <c r="AD16">
-        <v>5.65</v>
-      </c>
-      <c r="AE16">
+      <c r="Q17">
+        <v>2.5</v>
+      </c>
+      <c r="R17">
+        <v>1.69</v>
+      </c>
+      <c r="S17">
+        <v>2.3</v>
+      </c>
+      <c r="T17">
+        <v>4</v>
+      </c>
+      <c r="U17">
+        <v>1.18</v>
+      </c>
+      <c r="V17">
+        <v>11</v>
+      </c>
+      <c r="W17">
+        <v>1.04</v>
+      </c>
+      <c r="X17">
+        <v>1.13</v>
+      </c>
+      <c r="Y17">
+        <v>4.85</v>
+      </c>
+      <c r="Z17">
+        <v>1.74</v>
+      </c>
+      <c r="AA17">
+        <v>2.05</v>
+      </c>
+      <c r="AB17">
+        <v>3</v>
+      </c>
+      <c r="AC17">
+        <v>1.34</v>
+      </c>
+      <c r="AD17">
+        <v>6</v>
+      </c>
+      <c r="AE17">
         <v>1.11</v>
       </c>
-      <c r="AF16">
-        <v>2.3</v>
-      </c>
-      <c r="AG16">
-        <v>1.57</v>
-      </c>
-      <c r="AH16">
-        <v>11</v>
-      </c>
-      <c r="AI16">
-        <v>1.01</v>
-      </c>
-      <c r="AJ16" t="s">
-        <v>79</v>
-      </c>
-      <c r="AK16" t="s">
-        <v>79</v>
-      </c>
-      <c r="AL16" s="3">
+      <c r="AF17">
+        <v>2.45</v>
+      </c>
+      <c r="AG17">
+        <v>1.5</v>
+      </c>
+      <c r="AH17">
+        <v>12</v>
+      </c>
+      <c r="AI17">
+        <v>1</v>
+      </c>
+      <c r="AJ17" t="s">
+        <v>86</v>
+      </c>
+      <c r="AK17" t="s">
+        <v>86</v>
+      </c>
+      <c r="AL17" s="3">
         <v>45852.89583333334</v>
       </c>
     </row>

--- a/jogos_2025-07-14.xlsx
+++ b/jogos_2025-07-14.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="96">
   <si>
     <t>Date</t>
   </si>
@@ -199,27 +199,27 @@
     <t>Deportivo Riestra</t>
   </si>
   <si>
+    <t>Banfield</t>
+  </si>
+  <si>
     <t>Athletic Club</t>
   </si>
   <si>
-    <t>Banfield</t>
+    <t>Maringá</t>
   </si>
   <si>
     <t>Retrô</t>
   </si>
   <si>
-    <t>Maringá</t>
-  </si>
-  <si>
     <t>Juventude</t>
   </si>
   <si>
+    <t>Unión Santa Fe</t>
+  </si>
+  <si>
     <t>Vélez Sarsfield</t>
   </si>
   <si>
-    <t>Unión Santa Fe</t>
-  </si>
-  <si>
     <t>Botafogo SP</t>
   </si>
   <si>
@@ -238,49 +238,70 @@
     <t>Lanús</t>
   </si>
   <si>
+    <t>Defensa y Justicia</t>
+  </si>
+  <si>
     <t>Avaí</t>
   </si>
   <si>
-    <t>Defensa y Justicia</t>
+    <t>Brusque</t>
   </si>
   <si>
     <t>CSA</t>
   </si>
   <si>
-    <t>Brusque</t>
-  </si>
-  <si>
     <t>Sport Recife</t>
   </si>
   <si>
+    <t>Estudiantes</t>
+  </si>
+  <si>
     <t>Tigre</t>
   </si>
   <si>
-    <t>Estudiantes</t>
-  </si>
-  <si>
     <t>Volta Redonda</t>
   </si>
   <si>
     <t>complete</t>
   </si>
   <si>
-    <t>incomplete</t>
-  </si>
-  <si>
     <t>['22', '84', '89']</t>
   </si>
   <si>
     <t>['80']</t>
   </si>
   <si>
+    <t>['71']</t>
+  </si>
+  <si>
+    <t>['79']</t>
+  </si>
+  <si>
     <t>[]</t>
   </si>
   <si>
+    <t>['20', '9', '57', '84']</t>
+  </si>
+  <si>
+    <t>['12', '49']</t>
+  </si>
+  <si>
+    <t>['21']</t>
+  </si>
+  <si>
+    <t>['45', '45+4']</t>
+  </si>
+  <si>
     <t>['47', '74']</t>
   </si>
   <si>
     <t>['7', '16']</t>
+  </si>
+  <si>
+    <t>['63', '44']</t>
+  </si>
+  <si>
+    <t>['85']</t>
   </si>
 </sst>
 </file>
@@ -870,10 +891,10 @@
         <v>1.22</v>
       </c>
       <c r="AJ2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AK2" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="AL2" s="3">
         <v>45852.5</v>
@@ -986,10 +1007,10 @@
         <v>1.2</v>
       </c>
       <c r="AJ3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="AK3" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="AL3" s="3">
         <v>45852.58333333334</v>
@@ -1015,7 +1036,7 @@
         <v>71</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -1027,7 +1048,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L4">
         <v>3</v>
@@ -1102,10 +1123,10 @@
         <v>1.25</v>
       </c>
       <c r="AJ4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AK4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AL4" s="3">
         <v>45852.64583333334</v>
@@ -1131,7 +1152,7 @@
         <v>72</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -1143,7 +1164,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L5">
         <v>3.75</v>
@@ -1218,10 +1239,10 @@
         <v>1.6</v>
       </c>
       <c r="AJ5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AK5" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AL5" s="3">
         <v>45852.67708333334</v>
@@ -1247,7 +1268,7 @@
         <v>73</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -1259,7 +1280,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L6">
         <v>3.25</v>
@@ -1337,7 +1358,7 @@
         <v>86</v>
       </c>
       <c r="AK6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AL6" s="3">
         <v>45852.6875</v>
@@ -1351,7 +1372,7 @@
         <v>43</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D7" t="s">
         <v>55</v>
@@ -1375,40 +1396,40 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L7">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="M7">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="N7">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="O7">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="P7">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="Q7">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R7">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S7">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="T7">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U7">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="V7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="W7">
         <v>1.05</v>
@@ -1417,43 +1438,43 @@
         <v>1.1</v>
       </c>
       <c r="Y7">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Z7">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AA7">
+        <v>2.38</v>
+      </c>
+      <c r="AB7">
         <v>2.5</v>
       </c>
-      <c r="AB7">
-        <v>2.35</v>
-      </c>
       <c r="AC7">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AD7">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="AE7">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF7">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG7">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AH7">
         <v>9.5</v>
       </c>
       <c r="AI7">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AJ7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AK7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AL7" s="3">
         <v>45852.79166666666</v>
@@ -1473,10 +1494,10 @@
         <v>55</v>
       </c>
       <c r="E8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -1491,25 +1512,25 @@
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L8">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="M8">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="N8">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="O8">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="P8">
         <v>6.5</v>
       </c>
       <c r="Q8">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="R8">
         <v>1.53</v>
@@ -1548,10 +1569,10 @@
         <v>1.5</v>
       </c>
       <c r="AD8">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AE8">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF8">
         <v>2.05</v>
@@ -1566,10 +1587,10 @@
         <v>1.05</v>
       </c>
       <c r="AJ8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AK8" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AL8" s="3">
         <v>45852.79166666666</v>
@@ -1583,7 +1604,7 @@
         <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D9" t="s">
         <v>55</v>
@@ -1595,85 +1616,85 @@
         <v>75</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J9">
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L9">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="M9">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="N9">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="O9">
         <v>1.83</v>
       </c>
       <c r="P9">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="Q9">
         <v>2.4</v>
       </c>
       <c r="R9">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="S9">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="T9">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U9">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="V9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W9">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X9">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Y9">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="Z9">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AA9">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="AB9">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AC9">
         <v>1.5</v>
       </c>
       <c r="AD9">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="AE9">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF9">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG9">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AH9">
         <v>9.5</v>
@@ -1682,10 +1703,10 @@
         <v>1.05</v>
       </c>
       <c r="AJ9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="AK9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AL9" s="3">
         <v>45852.79166666666</v>
@@ -1714,94 +1735,94 @@
         <v>0</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10">
         <v>0</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L10">
-        <v>2.65</v>
+        <v>1.75</v>
       </c>
       <c r="M10">
-        <v>2.65</v>
+        <v>3.2</v>
       </c>
       <c r="N10">
-        <v>2.7</v>
+        <v>4.5</v>
       </c>
       <c r="O10">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="P10">
-        <v>5.5</v>
+        <v>8.1</v>
       </c>
       <c r="Q10">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="R10">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="S10">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="T10">
         <v>3.6</v>
       </c>
       <c r="U10">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="V10">
-        <v>10</v>
+        <v>9.25</v>
       </c>
       <c r="W10">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X10">
-        <v>1.11</v>
+        <v>1.03</v>
       </c>
       <c r="Y10">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="Z10">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AA10">
+        <v>2.4</v>
+      </c>
+      <c r="AB10">
         <v>2.38</v>
       </c>
-      <c r="AB10">
-        <v>2.7</v>
-      </c>
       <c r="AC10">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="AD10">
-        <v>5.35</v>
+        <v>4.5</v>
       </c>
       <c r="AE10">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF10">
         <v>2.15</v>
       </c>
       <c r="AG10">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AH10">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AI10">
         <v>1.02</v>
       </c>
       <c r="AJ10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AK10" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="AL10" s="3">
         <v>45852.8125</v>
@@ -1839,85 +1860,85 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L11">
-        <v>1.72</v>
+        <v>2.81</v>
       </c>
       <c r="M11">
-        <v>3.25</v>
+        <v>2.65</v>
       </c>
       <c r="N11">
-        <v>4.5</v>
+        <v>2.59</v>
       </c>
       <c r="O11">
+        <v>1.83</v>
+      </c>
+      <c r="P11">
+        <v>5.5</v>
+      </c>
+      <c r="Q11">
+        <v>2.4</v>
+      </c>
+      <c r="R11">
         <v>1.53</v>
       </c>
-      <c r="P11">
-        <v>8.1</v>
-      </c>
-      <c r="Q11">
-        <v>3.1</v>
-      </c>
-      <c r="R11">
-        <v>1.51</v>
-      </c>
       <c r="S11">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="T11">
         <v>3.6</v>
       </c>
       <c r="U11">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="V11">
-        <v>9.25</v>
+        <v>10</v>
       </c>
       <c r="W11">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="Y11">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="Z11">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AA11">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="AB11">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="AC11">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AD11">
-        <v>4.5</v>
+        <v>5.35</v>
       </c>
       <c r="AE11">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF11">
         <v>2.15</v>
       </c>
       <c r="AG11">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AH11">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AI11">
         <v>1.02</v>
       </c>
       <c r="AJ11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AK11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AL11" s="3">
         <v>45852.8125</v>
@@ -1943,28 +1964,28 @@
         <v>78</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12">
         <v>0</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12">
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L12">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="M12">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="N12">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O12">
         <v>1.83</v>
@@ -1976,28 +1997,28 @@
         <v>2.25</v>
       </c>
       <c r="R12">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="S12">
-        <v>2.4</v>
+        <v>2.64</v>
       </c>
       <c r="T12">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="U12">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="V12">
         <v>9.5</v>
       </c>
       <c r="W12">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X12">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y12">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="Z12">
         <v>1.4</v>
@@ -2015,7 +2036,7 @@
         <v>4.1</v>
       </c>
       <c r="AE12">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AF12">
         <v>1.95</v>
@@ -2030,10 +2051,10 @@
         <v>1.04</v>
       </c>
       <c r="AJ12" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="AK12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AL12" s="3">
         <v>45852.83333333334</v>
@@ -2059,97 +2080,97 @@
         <v>79</v>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13">
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L13">
-        <v>2.2</v>
+        <v>2.63</v>
       </c>
       <c r="M13">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="N13">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="O13">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="P13">
+        <v>6.5</v>
+      </c>
+      <c r="Q13">
+        <v>2.25</v>
+      </c>
+      <c r="R13">
+        <v>1.53</v>
+      </c>
+      <c r="S13">
+        <v>2.38</v>
+      </c>
+      <c r="T13">
+        <v>3.5</v>
+      </c>
+      <c r="U13">
+        <v>1.29</v>
+      </c>
+      <c r="V13">
+        <v>11</v>
+      </c>
+      <c r="W13">
+        <v>1.05</v>
+      </c>
+      <c r="X13">
+        <v>1.1</v>
+      </c>
+      <c r="Y13">
+        <v>6.5</v>
+      </c>
+      <c r="Z13">
+        <v>1.48</v>
+      </c>
+      <c r="AA13">
+        <v>2.43</v>
+      </c>
+      <c r="AB13">
+        <v>2.5</v>
+      </c>
+      <c r="AC13">
+        <v>1.5</v>
+      </c>
+      <c r="AD13">
         <v>5</v>
       </c>
-      <c r="Q13">
-        <v>2.88</v>
-      </c>
-      <c r="R13">
-        <v>1.67</v>
-      </c>
-      <c r="S13">
-        <v>2.1</v>
-      </c>
-      <c r="T13">
-        <v>4.33</v>
-      </c>
-      <c r="U13">
-        <v>1.2</v>
-      </c>
-      <c r="V13">
-        <v>15</v>
-      </c>
-      <c r="W13">
-        <v>1.03</v>
-      </c>
-      <c r="X13">
-        <v>1.14</v>
-      </c>
-      <c r="Y13">
-        <v>5.5</v>
-      </c>
-      <c r="Z13">
-        <v>1.58</v>
-      </c>
-      <c r="AA13">
-        <v>2.18</v>
-      </c>
-      <c r="AB13">
-        <v>3.1</v>
-      </c>
-      <c r="AC13">
-        <v>1.36</v>
-      </c>
-      <c r="AD13">
-        <v>6.5</v>
-      </c>
       <c r="AE13">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AF13">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AG13">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AH13">
-        <v>11</v>
+        <v>9.5</v>
       </c>
       <c r="AI13">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AJ13" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="AK13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AL13" s="3">
         <v>45852.88541666666</v>
@@ -2175,97 +2196,97 @@
         <v>79</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14">
         <v>0</v>
       </c>
       <c r="K14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L14">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="M14">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="N14">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="O14">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="P14">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="Q14">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="R14">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="S14">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="T14">
+        <v>3.75</v>
+      </c>
+      <c r="U14">
+        <v>1.25</v>
+      </c>
+      <c r="V14">
+        <v>11</v>
+      </c>
+      <c r="W14">
+        <v>1.05</v>
+      </c>
+      <c r="X14">
+        <v>1.11</v>
+      </c>
+      <c r="Y14">
+        <v>6.25</v>
+      </c>
+      <c r="Z14">
+        <v>1.48</v>
+      </c>
+      <c r="AA14">
+        <v>2.43</v>
+      </c>
+      <c r="AB14">
+        <v>2.6</v>
+      </c>
+      <c r="AC14">
+        <v>1.48</v>
+      </c>
+      <c r="AD14">
         <v>5</v>
       </c>
-      <c r="U14">
+      <c r="AE14">
         <v>1.17</v>
       </c>
-      <c r="V14">
-        <v>17</v>
-      </c>
-      <c r="W14">
-        <v>1.03</v>
-      </c>
-      <c r="X14">
-        <v>1.17</v>
-      </c>
-      <c r="Y14">
-        <v>5</v>
-      </c>
-      <c r="Z14">
-        <v>1.81</v>
-      </c>
-      <c r="AA14">
-        <v>2.07</v>
-      </c>
-      <c r="AB14">
-        <v>3.5</v>
-      </c>
-      <c r="AC14">
-        <v>1.3</v>
-      </c>
-      <c r="AD14">
-        <v>7</v>
-      </c>
-      <c r="AE14">
-        <v>1.09</v>
-      </c>
       <c r="AF14">
-        <v>2.63</v>
+        <v>2.05</v>
       </c>
       <c r="AG14">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AH14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI14">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AJ14" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="AK14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AL14" s="3">
         <v>45852.88541666666</v>
@@ -2291,97 +2312,97 @@
         <v>80</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15">
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L15">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="M15">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="N15">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="O15">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="P15">
+        <v>5</v>
+      </c>
+      <c r="Q15">
+        <v>2.88</v>
+      </c>
+      <c r="R15">
+        <v>1.67</v>
+      </c>
+      <c r="S15">
+        <v>2.1</v>
+      </c>
+      <c r="T15">
+        <v>4.33</v>
+      </c>
+      <c r="U15">
+        <v>1.2</v>
+      </c>
+      <c r="V15">
+        <v>15</v>
+      </c>
+      <c r="W15">
+        <v>1.03</v>
+      </c>
+      <c r="X15">
+        <v>1.14</v>
+      </c>
+      <c r="Y15">
+        <v>5.5</v>
+      </c>
+      <c r="Z15">
+        <v>1.58</v>
+      </c>
+      <c r="AA15">
+        <v>2.18</v>
+      </c>
+      <c r="AB15">
+        <v>3.1</v>
+      </c>
+      <c r="AC15">
+        <v>1.36</v>
+      </c>
+      <c r="AD15">
         <v>6.5</v>
       </c>
-      <c r="Q15">
-        <v>2.25</v>
-      </c>
-      <c r="R15">
-        <v>1.53</v>
-      </c>
-      <c r="S15">
-        <v>2.38</v>
-      </c>
-      <c r="T15">
-        <v>3.5</v>
-      </c>
-      <c r="U15">
-        <v>1.29</v>
-      </c>
-      <c r="V15">
+      <c r="AE15">
+        <v>1.1</v>
+      </c>
+      <c r="AF15">
+        <v>2.5</v>
+      </c>
+      <c r="AG15">
+        <v>1.5</v>
+      </c>
+      <c r="AH15">
         <v>11</v>
       </c>
-      <c r="W15">
-        <v>1.05</v>
-      </c>
-      <c r="X15">
-        <v>1.1</v>
-      </c>
-      <c r="Y15">
-        <v>6.5</v>
-      </c>
-      <c r="Z15">
-        <v>1.48</v>
-      </c>
-      <c r="AA15">
-        <v>2.43</v>
-      </c>
-      <c r="AB15">
-        <v>2.5</v>
-      </c>
-      <c r="AC15">
-        <v>1.5</v>
-      </c>
-      <c r="AD15">
-        <v>5</v>
-      </c>
-      <c r="AE15">
-        <v>1.17</v>
-      </c>
-      <c r="AF15">
-        <v>2</v>
-      </c>
-      <c r="AG15">
-        <v>1.75</v>
-      </c>
-      <c r="AH15">
-        <v>9.5</v>
-      </c>
       <c r="AI15">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AJ15" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="AK15" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="AL15" s="3">
         <v>45852.88541666666</v>
@@ -2407,97 +2428,97 @@
         <v>80</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J16">
         <v>0</v>
       </c>
       <c r="K16" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L16">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="M16">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="N16">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
       <c r="O16">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="P16">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="Q16">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="R16">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="S16">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="T16">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="U16">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="V16">
+        <v>17</v>
+      </c>
+      <c r="W16">
+        <v>1.03</v>
+      </c>
+      <c r="X16">
+        <v>1.17</v>
+      </c>
+      <c r="Y16">
+        <v>5</v>
+      </c>
+      <c r="Z16">
+        <v>1.81</v>
+      </c>
+      <c r="AA16">
+        <v>2.07</v>
+      </c>
+      <c r="AB16">
+        <v>3.5</v>
+      </c>
+      <c r="AC16">
+        <v>1.3</v>
+      </c>
+      <c r="AD16">
+        <v>7</v>
+      </c>
+      <c r="AE16">
+        <v>1.09</v>
+      </c>
+      <c r="AF16">
+        <v>2.63</v>
+      </c>
+      <c r="AG16">
+        <v>1.44</v>
+      </c>
+      <c r="AH16">
         <v>11</v>
       </c>
-      <c r="W16">
-        <v>1.05</v>
-      </c>
-      <c r="X16">
-        <v>1.11</v>
-      </c>
-      <c r="Y16">
-        <v>6.25</v>
-      </c>
-      <c r="Z16">
-        <v>1.48</v>
-      </c>
-      <c r="AA16">
-        <v>2.43</v>
-      </c>
-      <c r="AB16">
-        <v>2.6</v>
-      </c>
-      <c r="AC16">
-        <v>1.48</v>
-      </c>
-      <c r="AD16">
-        <v>5</v>
-      </c>
-      <c r="AE16">
-        <v>1.17</v>
-      </c>
-      <c r="AF16">
-        <v>2.05</v>
-      </c>
-      <c r="AG16">
-        <v>1.7</v>
-      </c>
-      <c r="AH16">
-        <v>10</v>
-      </c>
       <c r="AI16">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AJ16" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="AK16" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="AL16" s="3">
         <v>45852.88541666666</v>
@@ -2535,7 +2556,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="L17">
         <v>2.14</v>
@@ -2559,13 +2580,13 @@
         <v>1.69</v>
       </c>
       <c r="S17">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="T17">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="U17">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="V17">
         <v>11</v>
@@ -2577,10 +2598,10 @@
         <v>1.13</v>
       </c>
       <c r="Y17">
-        <v>4.85</v>
+        <v>5.3</v>
       </c>
       <c r="Z17">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AA17">
         <v>2.05</v>
@@ -2589,7 +2610,7 @@
         <v>3</v>
       </c>
       <c r="AC17">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AD17">
         <v>6</v>
@@ -2610,10 +2631,10 @@
         <v>1</v>
       </c>
       <c r="AJ17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AK17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AL17" s="3">
         <v>45852.89583333334</v>

--- a/jogos_2025-07-14.xlsx
+++ b/jogos_2025-07-14.xlsx
@@ -891,7 +891,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -901,19 +901,19 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -927,83 +927,83 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>4.15</v>
+        <v>3.3</v>
       </c>
       <c r="M4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N4" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="O4" t="n">
+        <v>4</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S4" t="n">
         <v>3.4</v>
       </c>
-      <c r="N4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="O4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.8</v>
-      </c>
       <c r="T4" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="V4" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X4" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>['80']</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>['7', '16']</t>
+        </is>
+      </c>
+      <c r="AG4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH4" t="n">
         <v>1.3</v>
       </c>
-      <c r="X4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>['11', '18', '86']</t>
-        </is>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AI4" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45852.58333333334</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,19 +1030,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="O5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X5" t="n">
         <v>3.3</v>
       </c>
-      <c r="M5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N5" t="n">
+      <c r="Y5" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC5" t="n">
         <v>1.89</v>
       </c>
-      <c r="O5" t="n">
-        <v>4</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W5" t="n">
+      <c r="AD5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>['11', '18', '86']</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
         <v>1.22</v>
       </c>
-      <c r="X5" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>['80']</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>['7', '16']</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AH5" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="AI5" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45852.58333333334</v>
@@ -1168,94 +1168,94 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['2', '11']</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['16', '43']</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Argentina Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,22 +1675,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Banfield</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Defensa y Justicia</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1701,65 +1701,65 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="M10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O10" t="n">
         <v>3</v>
       </c>
-      <c r="N10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O10" t="n">
-        <v>3.2</v>
-      </c>
       <c r="P10" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="Q10" t="n">
         <v>4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="S10" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="T10" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="U10" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="V10" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W10" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="X10" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="Z10" t="n">
         <v>1.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['20', '9', '57', '84']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -1771,7 +1771,7 @@
         <v>1.34</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AI10" t="n">
         <v>1.83</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Primera División</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,109 +1804,109 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Nacional Potosí</t>
+          <t>Banfield</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Real Oruro</t>
+          <t>Defensa y Justicia</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M11" t="n">
         <v>3</v>
       </c>
-      <c r="I11" t="n">
-        <v>2</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L11" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="M11" t="n">
-        <v>4.84</v>
-      </c>
       <c r="N11" t="n">
-        <v>6.12</v>
+        <v>3.3</v>
       </c>
       <c r="O11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X11" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AI11" t="n">
         <v>1.83</v>
       </c>
-      <c r="P11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>6</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S11" t="n">
-        <v>4</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X11" t="n">
-        <v>5</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>['13', '37']</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>['45', '84', '90+7']</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AJ11" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45852.79166666666</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,25 +1933,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Nacional Potosí</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Real Oruro</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
         <v>2</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1959,83 +1959,83 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.42</v>
+        <v>1.37</v>
       </c>
       <c r="M12" t="n">
-        <v>2.88</v>
+        <v>4.84</v>
       </c>
       <c r="N12" t="n">
-        <v>3.15</v>
+        <v>6.12</v>
       </c>
       <c r="O12" t="n">
-        <v>3</v>
+        <v>1.83</v>
       </c>
       <c r="P12" t="n">
-        <v>1.9</v>
+        <v>2.75</v>
       </c>
       <c r="Q12" t="n">
+        <v>6</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S12" t="n">
         <v>4</v>
       </c>
-      <c r="R12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.45</v>
-      </c>
       <c r="T12" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="U12" t="n">
-        <v>1.27</v>
+        <v>1.73</v>
       </c>
       <c r="V12" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X12" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y12" t="n">
         <v>1.44</v>
       </c>
-      <c r="X12" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>2.25</v>
-      </c>
       <c r="Z12" t="n">
-        <v>1.5</v>
+        <v>2.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.33</v>
+        <v>2.2</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.18</v>
+        <v>1.62</v>
       </c>
       <c r="AC12" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>['20', '9', '57', '84']</t>
+          <t>['13', '37']</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45', '84', '90+7']</t>
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.34</v>
+        <v>1.12</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.66</v>
+        <v>2.35</v>
       </c>
       <c r="AI12" t="n">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45852.79166666666</v>
@@ -2733,61 +2733,61 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="M18" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="N18" t="n">
         <v>4.1</v>
       </c>
       <c r="O18" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="P18" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Q18" t="n">
         <v>5</v>
       </c>
       <c r="R18" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="S18" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="T18" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="U18" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="V18" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="W18" t="n">
-        <v>1.58</v>
+        <v>1.81</v>
       </c>
       <c r="X18" t="n">
-        <v>2.18</v>
+        <v>2.07</v>
       </c>
       <c r="Y18" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AA18" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2800,16 +2800,16 @@
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AJ18" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45852.88541666666</v>
